--- a/Marketing/conversion-tracking/sheet/conversion-tracker.xlsx
+++ b/Marketing/conversion-tracking/sheet/conversion-tracker.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -904,8 +904,56 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SEO blog articles on salahalarm.com (one account per language)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>COUNTIF(Videos!$C:$C,A8)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIF(Videos!$C:$C,A8,Videos!$F:$F)</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUMIF(Videos!$C:$C,A8,Videos!$L:$L)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>SUMIF(Videos!$C:$C,A8,Videos!$M:$M)</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>SUMIF(Videos!$C:$C,A8,Videos!$N:$N)</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>IF(D8=0,"",E8/D8*1000)</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>IF(D8=0,"",F8/D8*10000)</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>IF(D8=0,"",G8/D8*10000)</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>IF(C8=0,"",D8/C8)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -915,7 +963,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -935,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1293,6 +1341,141 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>https://salahalarm.com/go/tt10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>seo-en</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>salahalarm.com/blog/en/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://salahalarm.com/go/seo-en</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>seo-ar</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>salahalarm.com/blog/ar/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://salahalarm.com/go/seo-ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>seo-tr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>salahalarm.com/blog/tr/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://salahalarm.com/go/seo-tr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>seo-id</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>salahalarm.com/blog/id/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://salahalarm.com/go/seo-id</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>seo-ur</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>salahalarm.com/blog/ur/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://salahalarm.com/go/seo-ur</t>
         </is>
       </c>
     </row>
@@ -14324,10 +14507,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Accounts!$A$2:$A$13</formula1>
+      <formula1>=Accounts!$A$2:$A$60</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"whatif,anim,alarm,pov,ramadan,mixed"</formula1>
+      <formula1>"whatif,anim,alarm,pov,ramadan,mixed,seo"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26894,7 +27077,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Accounts!$A$2:$A$13</formula1>
+      <formula1>=Accounts!$A$2:$A$60</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Marketing/conversion-tracking/sheet/conversion-tracker.xlsx
+++ b/Marketing/conversion-tracking/sheet/conversion-tracker.xlsx
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -81,12 +81,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -527,6 +527,20 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>Early signal: engagement_per_1k_views = (comments + shares + saves + profile visits) / views x 1000. It is available within hours;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   installs lag ~1 day. After a few days, check on the Formats tab whether it ranks formats the same way installs do before trusting it alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Rule of thumb: don't call a winner below ~30 installs per format; Apple hides very small campaign counts.</t>
         </is>
@@ -543,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -557,6 +571,7 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -615,6 +630,11 @@
           <t>views_per_video</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>engagement_per_1k_views</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -663,6 +683,10 @@
         <f>IF(C2=0,"",D2/C2)</f>
         <v/>
       </c>
+      <c r="L2" s="3">
+        <f>IF(D2=0,"",(SUMIF(Videos!$C:$C,A2,Videos!$P:$P)+SUMIF(Videos!$C:$C,A2,Videos!$H:$H)+SUMIF(Videos!$C:$C,A2,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A2,Videos!$I:$I))/D2*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -711,6 +735,10 @@
         <f>IF(C3=0,"",D3/C3)</f>
         <v/>
       </c>
+      <c r="L3" s="3">
+        <f>IF(D3=0,"",(SUMIF(Videos!$C:$C,A3,Videos!$P:$P)+SUMIF(Videos!$C:$C,A3,Videos!$H:$H)+SUMIF(Videos!$C:$C,A3,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A3,Videos!$I:$I))/D3*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -759,6 +787,10 @@
         <f>IF(C4=0,"",D4/C4)</f>
         <v/>
       </c>
+      <c r="L4" s="3">
+        <f>IF(D4=0,"",(SUMIF(Videos!$C:$C,A4,Videos!$P:$P)+SUMIF(Videos!$C:$C,A4,Videos!$H:$H)+SUMIF(Videos!$C:$C,A4,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A4,Videos!$I:$I))/D4*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -807,6 +839,10 @@
         <f>IF(C5=0,"",D5/C5)</f>
         <v/>
       </c>
+      <c r="L5" s="3">
+        <f>IF(D5=0,"",(SUMIF(Videos!$C:$C,A5,Videos!$P:$P)+SUMIF(Videos!$C:$C,A5,Videos!$H:$H)+SUMIF(Videos!$C:$C,A5,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A5,Videos!$I:$I))/D5*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -855,6 +891,10 @@
         <f>IF(C6=0,"",D6/C6)</f>
         <v/>
       </c>
+      <c r="L6" s="3">
+        <f>IF(D6=0,"",(SUMIF(Videos!$C:$C,A6,Videos!$P:$P)+SUMIF(Videos!$C:$C,A6,Videos!$H:$H)+SUMIF(Videos!$C:$C,A6,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A6,Videos!$I:$I))/D6*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -903,6 +943,10 @@
         <f>IF(C7=0,"",D7/C7)</f>
         <v/>
       </c>
+      <c r="L7" s="3">
+        <f>IF(D7=0,"",(SUMIF(Videos!$C:$C,A7,Videos!$P:$P)+SUMIF(Videos!$C:$C,A7,Videos!$H:$H)+SUMIF(Videos!$C:$C,A7,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A7,Videos!$I:$I))/D7*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -949,6 +993,10 @@
       </c>
       <c r="K8" s="5">
         <f>IF(C8=0,"",D8/C8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>IF(D8=0,"",(SUMIF(Videos!$C:$C,A8,Videos!$P:$P)+SUMIF(Videos!$C:$C,A8,Videos!$H:$H)+SUMIF(Videos!$C:$C,A8,Videos!$Q:$Q)+SUMIF(Videos!$C:$C,A8,Videos!$I:$I))/D8*1000)</f>
         <v/>
       </c>
     </row>
@@ -1490,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P401"/>
+  <dimension ref="A1:S401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1508,6 +1556,9 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1586,7 +1637,22 @@
           <t>installs_per_10k_views</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>saves</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>engagement_per_1k_views</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>← rows 2-5 and Daily rows 2-4 are SAMPLE data, delete before use</t>
         </is>
@@ -1651,6 +1717,16 @@
         <f>IF(OR(M2="",F2=0),"",M2/F2*10000)</f>
         <v/>
       </c>
+      <c r="P2" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="R2" s="3">
+        <f>IF(OR(F2="",F2=0),"",(N(P2)+N(H2)+N(Q2)+N(I2))/F2*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1711,6 +1787,16 @@
         <f>IF(OR(M3="",F3=0),"",M3/F3*10000)</f>
         <v/>
       </c>
+      <c r="P3" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="R3" s="3">
+        <f>IF(OR(F3="",F3=0),"",(N(P3)+N(H3)+N(Q3)+N(I3))/F3*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1771,6 +1857,16 @@
         <f>IF(OR(M4="",F4=0),"",M4/F4*10000)</f>
         <v/>
       </c>
+      <c r="P4" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="R4" s="3">
+        <f>IF(OR(F4="",F4=0),"",(N(P4)+N(H4)+N(Q4)+N(I4))/F4*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1829,6 +1925,16 @@
       </c>
       <c r="O5" s="3">
         <f>IF(OR(M5="",F5=0),"",M5/F5*10000)</f>
+        <v/>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="R5" s="3">
+        <f>IF(OR(F5="",F5=0),"",(N(P5)+N(H5)+N(Q5)+N(I5))/F5*1000)</f>
         <v/>
       </c>
     </row>
@@ -1863,6 +1969,12 @@
         <f>IF(OR(M6="",F6=0),"",M6/F6*10000)</f>
         <v/>
       </c>
+      <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="3">
+        <f>IF(OR(F6="",F6=0),"",(N(P6)+N(H6)+N(Q6)+N(I6))/F6*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -1895,6 +2007,12 @@
         <f>IF(OR(M7="",F7=0),"",M7/F7*10000)</f>
         <v/>
       </c>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="3">
+        <f>IF(OR(F7="",F7=0),"",(N(P7)+N(H7)+N(Q7)+N(I7))/F7*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -1927,6 +2045,12 @@
         <f>IF(OR(M8="",F8=0),"",M8/F8*10000)</f>
         <v/>
       </c>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="3">
+        <f>IF(OR(F8="",F8=0),"",(N(P8)+N(H8)+N(Q8)+N(I8))/F8*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -1959,6 +2083,12 @@
         <f>IF(OR(M9="",F9=0),"",M9/F9*10000)</f>
         <v/>
       </c>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="3">
+        <f>IF(OR(F9="",F9=0),"",(N(P9)+N(H9)+N(Q9)+N(I9))/F9*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -1991,6 +2121,12 @@
         <f>IF(OR(M10="",F10=0),"",M10/F10*10000)</f>
         <v/>
       </c>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="3">
+        <f>IF(OR(F10="",F10=0),"",(N(P10)+N(H10)+N(Q10)+N(I10))/F10*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -2023,6 +2159,12 @@
         <f>IF(OR(M11="",F11=0),"",M11/F11*10000)</f>
         <v/>
       </c>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="3">
+        <f>IF(OR(F11="",F11=0),"",(N(P11)+N(H11)+N(Q11)+N(I11))/F11*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -2055,6 +2197,12 @@
         <f>IF(OR(M12="",F12=0),"",M12/F12*10000)</f>
         <v/>
       </c>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="3">
+        <f>IF(OR(F12="",F12=0),"",(N(P12)+N(H12)+N(Q12)+N(I12))/F12*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -2087,6 +2235,12 @@
         <f>IF(OR(M13="",F13=0),"",M13/F13*10000)</f>
         <v/>
       </c>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="3">
+        <f>IF(OR(F13="",F13=0),"",(N(P13)+N(H13)+N(Q13)+N(I13))/F13*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -2119,6 +2273,12 @@
         <f>IF(OR(M14="",F14=0),"",M14/F14*10000)</f>
         <v/>
       </c>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="3">
+        <f>IF(OR(F14="",F14=0),"",(N(P14)+N(H14)+N(Q14)+N(I14))/F14*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -2151,6 +2311,12 @@
         <f>IF(OR(M15="",F15=0),"",M15/F15*10000)</f>
         <v/>
       </c>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="3">
+        <f>IF(OR(F15="",F15=0),"",(N(P15)+N(H15)+N(Q15)+N(I15))/F15*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -2183,6 +2349,12 @@
         <f>IF(OR(M16="",F16=0),"",M16/F16*10000)</f>
         <v/>
       </c>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="3">
+        <f>IF(OR(F16="",F16=0),"",(N(P16)+N(H16)+N(Q16)+N(I16))/F16*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -2215,6 +2387,12 @@
         <f>IF(OR(M17="",F17=0),"",M17/F17*10000)</f>
         <v/>
       </c>
+      <c r="P17" s="7" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="3">
+        <f>IF(OR(F17="",F17=0),"",(N(P17)+N(H17)+N(Q17)+N(I17))/F17*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -2247,6 +2425,12 @@
         <f>IF(OR(M18="",F18=0),"",M18/F18*10000)</f>
         <v/>
       </c>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="3">
+        <f>IF(OR(F18="",F18=0),"",(N(P18)+N(H18)+N(Q18)+N(I18))/F18*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -2279,6 +2463,12 @@
         <f>IF(OR(M19="",F19=0),"",M19/F19*10000)</f>
         <v/>
       </c>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="3">
+        <f>IF(OR(F19="",F19=0),"",(N(P19)+N(H19)+N(Q19)+N(I19))/F19*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -2311,6 +2501,12 @@
         <f>IF(OR(M20="",F20=0),"",M20/F20*10000)</f>
         <v/>
       </c>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="3">
+        <f>IF(OR(F20="",F20=0),"",(N(P20)+N(H20)+N(Q20)+N(I20))/F20*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -2343,6 +2539,12 @@
         <f>IF(OR(M21="",F21=0),"",M21/F21*10000)</f>
         <v/>
       </c>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="3">
+        <f>IF(OR(F21="",F21=0),"",(N(P21)+N(H21)+N(Q21)+N(I21))/F21*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -2375,6 +2577,12 @@
         <f>IF(OR(M22="",F22=0),"",M22/F22*10000)</f>
         <v/>
       </c>
+      <c r="P22" s="7" t="n"/>
+      <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="3">
+        <f>IF(OR(F22="",F22=0),"",(N(P22)+N(H22)+N(Q22)+N(I22))/F22*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -2407,6 +2615,12 @@
         <f>IF(OR(M23="",F23=0),"",M23/F23*10000)</f>
         <v/>
       </c>
+      <c r="P23" s="7" t="n"/>
+      <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="3">
+        <f>IF(OR(F23="",F23=0),"",(N(P23)+N(H23)+N(Q23)+N(I23))/F23*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -2439,6 +2653,12 @@
         <f>IF(OR(M24="",F24=0),"",M24/F24*10000)</f>
         <v/>
       </c>
+      <c r="P24" s="7" t="n"/>
+      <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="3">
+        <f>IF(OR(F24="",F24=0),"",(N(P24)+N(H24)+N(Q24)+N(I24))/F24*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -2471,6 +2691,12 @@
         <f>IF(OR(M25="",F25=0),"",M25/F25*10000)</f>
         <v/>
       </c>
+      <c r="P25" s="7" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="3">
+        <f>IF(OR(F25="",F25=0),"",(N(P25)+N(H25)+N(Q25)+N(I25))/F25*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -2503,6 +2729,12 @@
         <f>IF(OR(M26="",F26=0),"",M26/F26*10000)</f>
         <v/>
       </c>
+      <c r="P26" s="7" t="n"/>
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="3">
+        <f>IF(OR(F26="",F26=0),"",(N(P26)+N(H26)+N(Q26)+N(I26))/F26*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -2535,6 +2767,12 @@
         <f>IF(OR(M27="",F27=0),"",M27/F27*10000)</f>
         <v/>
       </c>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="3">
+        <f>IF(OR(F27="",F27=0),"",(N(P27)+N(H27)+N(Q27)+N(I27))/F27*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -2567,6 +2805,12 @@
         <f>IF(OR(M28="",F28=0),"",M28/F28*10000)</f>
         <v/>
       </c>
+      <c r="P28" s="7" t="n"/>
+      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="3">
+        <f>IF(OR(F28="",F28=0),"",(N(P28)+N(H28)+N(Q28)+N(I28))/F28*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -2599,6 +2843,12 @@
         <f>IF(OR(M29="",F29=0),"",M29/F29*10000)</f>
         <v/>
       </c>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="3">
+        <f>IF(OR(F29="",F29=0),"",(N(P29)+N(H29)+N(Q29)+N(I29))/F29*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -2631,6 +2881,12 @@
         <f>IF(OR(M30="",F30=0),"",M30/F30*10000)</f>
         <v/>
       </c>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="3">
+        <f>IF(OR(F30="",F30=0),"",(N(P30)+N(H30)+N(Q30)+N(I30))/F30*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -2663,6 +2919,12 @@
         <f>IF(OR(M31="",F31=0),"",M31/F31*10000)</f>
         <v/>
       </c>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="3">
+        <f>IF(OR(F31="",F31=0),"",(N(P31)+N(H31)+N(Q31)+N(I31))/F31*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -2695,6 +2957,12 @@
         <f>IF(OR(M32="",F32=0),"",M32/F32*10000)</f>
         <v/>
       </c>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="3">
+        <f>IF(OR(F32="",F32=0),"",(N(P32)+N(H32)+N(Q32)+N(I32))/F32*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -2727,6 +2995,12 @@
         <f>IF(OR(M33="",F33=0),"",M33/F33*10000)</f>
         <v/>
       </c>
+      <c r="P33" s="7" t="n"/>
+      <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="3">
+        <f>IF(OR(F33="",F33=0),"",(N(P33)+N(H33)+N(Q33)+N(I33))/F33*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -2759,6 +3033,12 @@
         <f>IF(OR(M34="",F34=0),"",M34/F34*10000)</f>
         <v/>
       </c>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="3">
+        <f>IF(OR(F34="",F34=0),"",(N(P34)+N(H34)+N(Q34)+N(I34))/F34*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -2791,6 +3071,12 @@
         <f>IF(OR(M35="",F35=0),"",M35/F35*10000)</f>
         <v/>
       </c>
+      <c r="P35" s="7" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="3">
+        <f>IF(OR(F35="",F35=0),"",(N(P35)+N(H35)+N(Q35)+N(I35))/F35*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -2823,6 +3109,12 @@
         <f>IF(OR(M36="",F36=0),"",M36/F36*10000)</f>
         <v/>
       </c>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="3">
+        <f>IF(OR(F36="",F36=0),"",(N(P36)+N(H36)+N(Q36)+N(I36))/F36*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -2855,6 +3147,12 @@
         <f>IF(OR(M37="",F37=0),"",M37/F37*10000)</f>
         <v/>
       </c>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="3">
+        <f>IF(OR(F37="",F37=0),"",(N(P37)+N(H37)+N(Q37)+N(I37))/F37*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -2887,6 +3185,12 @@
         <f>IF(OR(M38="",F38=0),"",M38/F38*10000)</f>
         <v/>
       </c>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="3">
+        <f>IF(OR(F38="",F38=0),"",(N(P38)+N(H38)+N(Q38)+N(I38))/F38*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -2919,6 +3223,12 @@
         <f>IF(OR(M39="",F39=0),"",M39/F39*10000)</f>
         <v/>
       </c>
+      <c r="P39" s="7" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="3">
+        <f>IF(OR(F39="",F39=0),"",(N(P39)+N(H39)+N(Q39)+N(I39))/F39*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -2951,6 +3261,12 @@
         <f>IF(OR(M40="",F40=0),"",M40/F40*10000)</f>
         <v/>
       </c>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="3">
+        <f>IF(OR(F40="",F40=0),"",(N(P40)+N(H40)+N(Q40)+N(I40))/F40*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -2983,6 +3299,12 @@
         <f>IF(OR(M41="",F41=0),"",M41/F41*10000)</f>
         <v/>
       </c>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="3">
+        <f>IF(OR(F41="",F41=0),"",(N(P41)+N(H41)+N(Q41)+N(I41))/F41*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -3015,6 +3337,12 @@
         <f>IF(OR(M42="",F42=0),"",M42/F42*10000)</f>
         <v/>
       </c>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="3">
+        <f>IF(OR(F42="",F42=0),"",(N(P42)+N(H42)+N(Q42)+N(I42))/F42*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -3047,6 +3375,12 @@
         <f>IF(OR(M43="",F43=0),"",M43/F43*10000)</f>
         <v/>
       </c>
+      <c r="P43" s="7" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="3">
+        <f>IF(OR(F43="",F43=0),"",(N(P43)+N(H43)+N(Q43)+N(I43))/F43*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -3079,6 +3413,12 @@
         <f>IF(OR(M44="",F44=0),"",M44/F44*10000)</f>
         <v/>
       </c>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="3">
+        <f>IF(OR(F44="",F44=0),"",(N(P44)+N(H44)+N(Q44)+N(I44))/F44*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -3111,6 +3451,12 @@
         <f>IF(OR(M45="",F45=0),"",M45/F45*10000)</f>
         <v/>
       </c>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="3">
+        <f>IF(OR(F45="",F45=0),"",(N(P45)+N(H45)+N(Q45)+N(I45))/F45*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -3143,6 +3489,12 @@
         <f>IF(OR(M46="",F46=0),"",M46/F46*10000)</f>
         <v/>
       </c>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="3">
+        <f>IF(OR(F46="",F46=0),"",(N(P46)+N(H46)+N(Q46)+N(I46))/F46*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -3175,6 +3527,12 @@
         <f>IF(OR(M47="",F47=0),"",M47/F47*10000)</f>
         <v/>
       </c>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="3">
+        <f>IF(OR(F47="",F47=0),"",(N(P47)+N(H47)+N(Q47)+N(I47))/F47*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -3207,6 +3565,12 @@
         <f>IF(OR(M48="",F48=0),"",M48/F48*10000)</f>
         <v/>
       </c>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="3">
+        <f>IF(OR(F48="",F48=0),"",(N(P48)+N(H48)+N(Q48)+N(I48))/F48*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -3239,6 +3603,12 @@
         <f>IF(OR(M49="",F49=0),"",M49/F49*10000)</f>
         <v/>
       </c>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="3">
+        <f>IF(OR(F49="",F49=0),"",(N(P49)+N(H49)+N(Q49)+N(I49))/F49*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -3271,6 +3641,12 @@
         <f>IF(OR(M50="",F50=0),"",M50/F50*10000)</f>
         <v/>
       </c>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="3">
+        <f>IF(OR(F50="",F50=0),"",(N(P50)+N(H50)+N(Q50)+N(I50))/F50*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -3303,6 +3679,12 @@
         <f>IF(OR(M51="",F51=0),"",M51/F51*10000)</f>
         <v/>
       </c>
+      <c r="P51" s="7" t="n"/>
+      <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="3">
+        <f>IF(OR(F51="",F51=0),"",(N(P51)+N(H51)+N(Q51)+N(I51))/F51*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -3335,6 +3717,12 @@
         <f>IF(OR(M52="",F52=0),"",M52/F52*10000)</f>
         <v/>
       </c>
+      <c r="P52" s="7" t="n"/>
+      <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="3">
+        <f>IF(OR(F52="",F52=0),"",(N(P52)+N(H52)+N(Q52)+N(I52))/F52*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -3367,6 +3755,12 @@
         <f>IF(OR(M53="",F53=0),"",M53/F53*10000)</f>
         <v/>
       </c>
+      <c r="P53" s="7" t="n"/>
+      <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="3">
+        <f>IF(OR(F53="",F53=0),"",(N(P53)+N(H53)+N(Q53)+N(I53))/F53*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -3399,6 +3793,12 @@
         <f>IF(OR(M54="",F54=0),"",M54/F54*10000)</f>
         <v/>
       </c>
+      <c r="P54" s="7" t="n"/>
+      <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="3">
+        <f>IF(OR(F54="",F54=0),"",(N(P54)+N(H54)+N(Q54)+N(I54))/F54*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -3431,6 +3831,12 @@
         <f>IF(OR(M55="",F55=0),"",M55/F55*10000)</f>
         <v/>
       </c>
+      <c r="P55" s="7" t="n"/>
+      <c r="Q55" s="7" t="n"/>
+      <c r="R55" s="3">
+        <f>IF(OR(F55="",F55=0),"",(N(P55)+N(H55)+N(Q55)+N(I55))/F55*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -3463,6 +3869,12 @@
         <f>IF(OR(M56="",F56=0),"",M56/F56*10000)</f>
         <v/>
       </c>
+      <c r="P56" s="7" t="n"/>
+      <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="3">
+        <f>IF(OR(F56="",F56=0),"",(N(P56)+N(H56)+N(Q56)+N(I56))/F56*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -3495,6 +3907,12 @@
         <f>IF(OR(M57="",F57=0),"",M57/F57*10000)</f>
         <v/>
       </c>
+      <c r="P57" s="7" t="n"/>
+      <c r="Q57" s="7" t="n"/>
+      <c r="R57" s="3">
+        <f>IF(OR(F57="",F57=0),"",(N(P57)+N(H57)+N(Q57)+N(I57))/F57*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -3527,6 +3945,12 @@
         <f>IF(OR(M58="",F58=0),"",M58/F58*10000)</f>
         <v/>
       </c>
+      <c r="P58" s="7" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="3">
+        <f>IF(OR(F58="",F58=0),"",(N(P58)+N(H58)+N(Q58)+N(I58))/F58*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -3559,6 +3983,12 @@
         <f>IF(OR(M59="",F59=0),"",M59/F59*10000)</f>
         <v/>
       </c>
+      <c r="P59" s="7" t="n"/>
+      <c r="Q59" s="7" t="n"/>
+      <c r="R59" s="3">
+        <f>IF(OR(F59="",F59=0),"",(N(P59)+N(H59)+N(Q59)+N(I59))/F59*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -3591,6 +4021,12 @@
         <f>IF(OR(M60="",F60=0),"",M60/F60*10000)</f>
         <v/>
       </c>
+      <c r="P60" s="7" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="3">
+        <f>IF(OR(F60="",F60=0),"",(N(P60)+N(H60)+N(Q60)+N(I60))/F60*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -3623,6 +4059,12 @@
         <f>IF(OR(M61="",F61=0),"",M61/F61*10000)</f>
         <v/>
       </c>
+      <c r="P61" s="7" t="n"/>
+      <c r="Q61" s="7" t="n"/>
+      <c r="R61" s="3">
+        <f>IF(OR(F61="",F61=0),"",(N(P61)+N(H61)+N(Q61)+N(I61))/F61*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -3655,6 +4097,12 @@
         <f>IF(OR(M62="",F62=0),"",M62/F62*10000)</f>
         <v/>
       </c>
+      <c r="P62" s="7" t="n"/>
+      <c r="Q62" s="7" t="n"/>
+      <c r="R62" s="3">
+        <f>IF(OR(F62="",F62=0),"",(N(P62)+N(H62)+N(Q62)+N(I62))/F62*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -3687,6 +4135,12 @@
         <f>IF(OR(M63="",F63=0),"",M63/F63*10000)</f>
         <v/>
       </c>
+      <c r="P63" s="7" t="n"/>
+      <c r="Q63" s="7" t="n"/>
+      <c r="R63" s="3">
+        <f>IF(OR(F63="",F63=0),"",(N(P63)+N(H63)+N(Q63)+N(I63))/F63*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -3719,6 +4173,12 @@
         <f>IF(OR(M64="",F64=0),"",M64/F64*10000)</f>
         <v/>
       </c>
+      <c r="P64" s="7" t="n"/>
+      <c r="Q64" s="7" t="n"/>
+      <c r="R64" s="3">
+        <f>IF(OR(F64="",F64=0),"",(N(P64)+N(H64)+N(Q64)+N(I64))/F64*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -3751,6 +4211,12 @@
         <f>IF(OR(M65="",F65=0),"",M65/F65*10000)</f>
         <v/>
       </c>
+      <c r="P65" s="7" t="n"/>
+      <c r="Q65" s="7" t="n"/>
+      <c r="R65" s="3">
+        <f>IF(OR(F65="",F65=0),"",(N(P65)+N(H65)+N(Q65)+N(I65))/F65*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -3783,6 +4249,12 @@
         <f>IF(OR(M66="",F66=0),"",M66/F66*10000)</f>
         <v/>
       </c>
+      <c r="P66" s="7" t="n"/>
+      <c r="Q66" s="7" t="n"/>
+      <c r="R66" s="3">
+        <f>IF(OR(F66="",F66=0),"",(N(P66)+N(H66)+N(Q66)+N(I66))/F66*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -3815,6 +4287,12 @@
         <f>IF(OR(M67="",F67=0),"",M67/F67*10000)</f>
         <v/>
       </c>
+      <c r="P67" s="7" t="n"/>
+      <c r="Q67" s="7" t="n"/>
+      <c r="R67" s="3">
+        <f>IF(OR(F67="",F67=0),"",(N(P67)+N(H67)+N(Q67)+N(I67))/F67*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -3847,6 +4325,12 @@
         <f>IF(OR(M68="",F68=0),"",M68/F68*10000)</f>
         <v/>
       </c>
+      <c r="P68" s="7" t="n"/>
+      <c r="Q68" s="7" t="n"/>
+      <c r="R68" s="3">
+        <f>IF(OR(F68="",F68=0),"",(N(P68)+N(H68)+N(Q68)+N(I68))/F68*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -3879,6 +4363,12 @@
         <f>IF(OR(M69="",F69=0),"",M69/F69*10000)</f>
         <v/>
       </c>
+      <c r="P69" s="7" t="n"/>
+      <c r="Q69" s="7" t="n"/>
+      <c r="R69" s="3">
+        <f>IF(OR(F69="",F69=0),"",(N(P69)+N(H69)+N(Q69)+N(I69))/F69*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -3911,6 +4401,12 @@
         <f>IF(OR(M70="",F70=0),"",M70/F70*10000)</f>
         <v/>
       </c>
+      <c r="P70" s="7" t="n"/>
+      <c r="Q70" s="7" t="n"/>
+      <c r="R70" s="3">
+        <f>IF(OR(F70="",F70=0),"",(N(P70)+N(H70)+N(Q70)+N(I70))/F70*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -3943,6 +4439,12 @@
         <f>IF(OR(M71="",F71=0),"",M71/F71*10000)</f>
         <v/>
       </c>
+      <c r="P71" s="7" t="n"/>
+      <c r="Q71" s="7" t="n"/>
+      <c r="R71" s="3">
+        <f>IF(OR(F71="",F71=0),"",(N(P71)+N(H71)+N(Q71)+N(I71))/F71*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -3975,6 +4477,12 @@
         <f>IF(OR(M72="",F72=0),"",M72/F72*10000)</f>
         <v/>
       </c>
+      <c r="P72" s="7" t="n"/>
+      <c r="Q72" s="7" t="n"/>
+      <c r="R72" s="3">
+        <f>IF(OR(F72="",F72=0),"",(N(P72)+N(H72)+N(Q72)+N(I72))/F72*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -4007,6 +4515,12 @@
         <f>IF(OR(M73="",F73=0),"",M73/F73*10000)</f>
         <v/>
       </c>
+      <c r="P73" s="7" t="n"/>
+      <c r="Q73" s="7" t="n"/>
+      <c r="R73" s="3">
+        <f>IF(OR(F73="",F73=0),"",(N(P73)+N(H73)+N(Q73)+N(I73))/F73*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -4039,6 +4553,12 @@
         <f>IF(OR(M74="",F74=0),"",M74/F74*10000)</f>
         <v/>
       </c>
+      <c r="P74" s="7" t="n"/>
+      <c r="Q74" s="7" t="n"/>
+      <c r="R74" s="3">
+        <f>IF(OR(F74="",F74=0),"",(N(P74)+N(H74)+N(Q74)+N(I74))/F74*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -4071,6 +4591,12 @@
         <f>IF(OR(M75="",F75=0),"",M75/F75*10000)</f>
         <v/>
       </c>
+      <c r="P75" s="7" t="n"/>
+      <c r="Q75" s="7" t="n"/>
+      <c r="R75" s="3">
+        <f>IF(OR(F75="",F75=0),"",(N(P75)+N(H75)+N(Q75)+N(I75))/F75*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -4103,6 +4629,12 @@
         <f>IF(OR(M76="",F76=0),"",M76/F76*10000)</f>
         <v/>
       </c>
+      <c r="P76" s="7" t="n"/>
+      <c r="Q76" s="7" t="n"/>
+      <c r="R76" s="3">
+        <f>IF(OR(F76="",F76=0),"",(N(P76)+N(H76)+N(Q76)+N(I76))/F76*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -4135,6 +4667,12 @@
         <f>IF(OR(M77="",F77=0),"",M77/F77*10000)</f>
         <v/>
       </c>
+      <c r="P77" s="7" t="n"/>
+      <c r="Q77" s="7" t="n"/>
+      <c r="R77" s="3">
+        <f>IF(OR(F77="",F77=0),"",(N(P77)+N(H77)+N(Q77)+N(I77))/F77*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -4167,6 +4705,12 @@
         <f>IF(OR(M78="",F78=0),"",M78/F78*10000)</f>
         <v/>
       </c>
+      <c r="P78" s="7" t="n"/>
+      <c r="Q78" s="7" t="n"/>
+      <c r="R78" s="3">
+        <f>IF(OR(F78="",F78=0),"",(N(P78)+N(H78)+N(Q78)+N(I78))/F78*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -4199,6 +4743,12 @@
         <f>IF(OR(M79="",F79=0),"",M79/F79*10000)</f>
         <v/>
       </c>
+      <c r="P79" s="7" t="n"/>
+      <c r="Q79" s="7" t="n"/>
+      <c r="R79" s="3">
+        <f>IF(OR(F79="",F79=0),"",(N(P79)+N(H79)+N(Q79)+N(I79))/F79*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -4231,6 +4781,12 @@
         <f>IF(OR(M80="",F80=0),"",M80/F80*10000)</f>
         <v/>
       </c>
+      <c r="P80" s="7" t="n"/>
+      <c r="Q80" s="7" t="n"/>
+      <c r="R80" s="3">
+        <f>IF(OR(F80="",F80=0),"",(N(P80)+N(H80)+N(Q80)+N(I80))/F80*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -4263,6 +4819,12 @@
         <f>IF(OR(M81="",F81=0),"",M81/F81*10000)</f>
         <v/>
       </c>
+      <c r="P81" s="7" t="n"/>
+      <c r="Q81" s="7" t="n"/>
+      <c r="R81" s="3">
+        <f>IF(OR(F81="",F81=0),"",(N(P81)+N(H81)+N(Q81)+N(I81))/F81*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -4295,6 +4857,12 @@
         <f>IF(OR(M82="",F82=0),"",M82/F82*10000)</f>
         <v/>
       </c>
+      <c r="P82" s="7" t="n"/>
+      <c r="Q82" s="7" t="n"/>
+      <c r="R82" s="3">
+        <f>IF(OR(F82="",F82=0),"",(N(P82)+N(H82)+N(Q82)+N(I82))/F82*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -4327,6 +4895,12 @@
         <f>IF(OR(M83="",F83=0),"",M83/F83*10000)</f>
         <v/>
       </c>
+      <c r="P83" s="7" t="n"/>
+      <c r="Q83" s="7" t="n"/>
+      <c r="R83" s="3">
+        <f>IF(OR(F83="",F83=0),"",(N(P83)+N(H83)+N(Q83)+N(I83))/F83*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -4359,6 +4933,12 @@
         <f>IF(OR(M84="",F84=0),"",M84/F84*10000)</f>
         <v/>
       </c>
+      <c r="P84" s="7" t="n"/>
+      <c r="Q84" s="7" t="n"/>
+      <c r="R84" s="3">
+        <f>IF(OR(F84="",F84=0),"",(N(P84)+N(H84)+N(Q84)+N(I84))/F84*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -4391,6 +4971,12 @@
         <f>IF(OR(M85="",F85=0),"",M85/F85*10000)</f>
         <v/>
       </c>
+      <c r="P85" s="7" t="n"/>
+      <c r="Q85" s="7" t="n"/>
+      <c r="R85" s="3">
+        <f>IF(OR(F85="",F85=0),"",(N(P85)+N(H85)+N(Q85)+N(I85))/F85*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -4423,6 +5009,12 @@
         <f>IF(OR(M86="",F86=0),"",M86/F86*10000)</f>
         <v/>
       </c>
+      <c r="P86" s="7" t="n"/>
+      <c r="Q86" s="7" t="n"/>
+      <c r="R86" s="3">
+        <f>IF(OR(F86="",F86=0),"",(N(P86)+N(H86)+N(Q86)+N(I86))/F86*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -4455,6 +5047,12 @@
         <f>IF(OR(M87="",F87=0),"",M87/F87*10000)</f>
         <v/>
       </c>
+      <c r="P87" s="7" t="n"/>
+      <c r="Q87" s="7" t="n"/>
+      <c r="R87" s="3">
+        <f>IF(OR(F87="",F87=0),"",(N(P87)+N(H87)+N(Q87)+N(I87))/F87*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -4487,6 +5085,12 @@
         <f>IF(OR(M88="",F88=0),"",M88/F88*10000)</f>
         <v/>
       </c>
+      <c r="P88" s="7" t="n"/>
+      <c r="Q88" s="7" t="n"/>
+      <c r="R88" s="3">
+        <f>IF(OR(F88="",F88=0),"",(N(P88)+N(H88)+N(Q88)+N(I88))/F88*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -4519,6 +5123,12 @@
         <f>IF(OR(M89="",F89=0),"",M89/F89*10000)</f>
         <v/>
       </c>
+      <c r="P89" s="7" t="n"/>
+      <c r="Q89" s="7" t="n"/>
+      <c r="R89" s="3">
+        <f>IF(OR(F89="",F89=0),"",(N(P89)+N(H89)+N(Q89)+N(I89))/F89*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -4551,6 +5161,12 @@
         <f>IF(OR(M90="",F90=0),"",M90/F90*10000)</f>
         <v/>
       </c>
+      <c r="P90" s="7" t="n"/>
+      <c r="Q90" s="7" t="n"/>
+      <c r="R90" s="3">
+        <f>IF(OR(F90="",F90=0),"",(N(P90)+N(H90)+N(Q90)+N(I90))/F90*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -4583,6 +5199,12 @@
         <f>IF(OR(M91="",F91=0),"",M91/F91*10000)</f>
         <v/>
       </c>
+      <c r="P91" s="7" t="n"/>
+      <c r="Q91" s="7" t="n"/>
+      <c r="R91" s="3">
+        <f>IF(OR(F91="",F91=0),"",(N(P91)+N(H91)+N(Q91)+N(I91))/F91*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -4615,6 +5237,12 @@
         <f>IF(OR(M92="",F92=0),"",M92/F92*10000)</f>
         <v/>
       </c>
+      <c r="P92" s="7" t="n"/>
+      <c r="Q92" s="7" t="n"/>
+      <c r="R92" s="3">
+        <f>IF(OR(F92="",F92=0),"",(N(P92)+N(H92)+N(Q92)+N(I92))/F92*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -4647,6 +5275,12 @@
         <f>IF(OR(M93="",F93=0),"",M93/F93*10000)</f>
         <v/>
       </c>
+      <c r="P93" s="7" t="n"/>
+      <c r="Q93" s="7" t="n"/>
+      <c r="R93" s="3">
+        <f>IF(OR(F93="",F93=0),"",(N(P93)+N(H93)+N(Q93)+N(I93))/F93*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -4679,6 +5313,12 @@
         <f>IF(OR(M94="",F94=0),"",M94/F94*10000)</f>
         <v/>
       </c>
+      <c r="P94" s="7" t="n"/>
+      <c r="Q94" s="7" t="n"/>
+      <c r="R94" s="3">
+        <f>IF(OR(F94="",F94=0),"",(N(P94)+N(H94)+N(Q94)+N(I94))/F94*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -4711,6 +5351,12 @@
         <f>IF(OR(M95="",F95=0),"",M95/F95*10000)</f>
         <v/>
       </c>
+      <c r="P95" s="7" t="n"/>
+      <c r="Q95" s="7" t="n"/>
+      <c r="R95" s="3">
+        <f>IF(OR(F95="",F95=0),"",(N(P95)+N(H95)+N(Q95)+N(I95))/F95*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -4743,6 +5389,12 @@
         <f>IF(OR(M96="",F96=0),"",M96/F96*10000)</f>
         <v/>
       </c>
+      <c r="P96" s="7" t="n"/>
+      <c r="Q96" s="7" t="n"/>
+      <c r="R96" s="3">
+        <f>IF(OR(F96="",F96=0),"",(N(P96)+N(H96)+N(Q96)+N(I96))/F96*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -4775,6 +5427,12 @@
         <f>IF(OR(M97="",F97=0),"",M97/F97*10000)</f>
         <v/>
       </c>
+      <c r="P97" s="7" t="n"/>
+      <c r="Q97" s="7" t="n"/>
+      <c r="R97" s="3">
+        <f>IF(OR(F97="",F97=0),"",(N(P97)+N(H97)+N(Q97)+N(I97))/F97*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -4807,6 +5465,12 @@
         <f>IF(OR(M98="",F98=0),"",M98/F98*10000)</f>
         <v/>
       </c>
+      <c r="P98" s="7" t="n"/>
+      <c r="Q98" s="7" t="n"/>
+      <c r="R98" s="3">
+        <f>IF(OR(F98="",F98=0),"",(N(P98)+N(H98)+N(Q98)+N(I98))/F98*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -4839,6 +5503,12 @@
         <f>IF(OR(M99="",F99=0),"",M99/F99*10000)</f>
         <v/>
       </c>
+      <c r="P99" s="7" t="n"/>
+      <c r="Q99" s="7" t="n"/>
+      <c r="R99" s="3">
+        <f>IF(OR(F99="",F99=0),"",(N(P99)+N(H99)+N(Q99)+N(I99))/F99*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -4871,6 +5541,12 @@
         <f>IF(OR(M100="",F100=0),"",M100/F100*10000)</f>
         <v/>
       </c>
+      <c r="P100" s="7" t="n"/>
+      <c r="Q100" s="7" t="n"/>
+      <c r="R100" s="3">
+        <f>IF(OR(F100="",F100=0),"",(N(P100)+N(H100)+N(Q100)+N(I100))/F100*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -4903,6 +5579,12 @@
         <f>IF(OR(M101="",F101=0),"",M101/F101*10000)</f>
         <v/>
       </c>
+      <c r="P101" s="7" t="n"/>
+      <c r="Q101" s="7" t="n"/>
+      <c r="R101" s="3">
+        <f>IF(OR(F101="",F101=0),"",(N(P101)+N(H101)+N(Q101)+N(I101))/F101*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -4935,6 +5617,12 @@
         <f>IF(OR(M102="",F102=0),"",M102/F102*10000)</f>
         <v/>
       </c>
+      <c r="P102" s="7" t="n"/>
+      <c r="Q102" s="7" t="n"/>
+      <c r="R102" s="3">
+        <f>IF(OR(F102="",F102=0),"",(N(P102)+N(H102)+N(Q102)+N(I102))/F102*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -4967,6 +5655,12 @@
         <f>IF(OR(M103="",F103=0),"",M103/F103*10000)</f>
         <v/>
       </c>
+      <c r="P103" s="7" t="n"/>
+      <c r="Q103" s="7" t="n"/>
+      <c r="R103" s="3">
+        <f>IF(OR(F103="",F103=0),"",(N(P103)+N(H103)+N(Q103)+N(I103))/F103*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -4999,6 +5693,12 @@
         <f>IF(OR(M104="",F104=0),"",M104/F104*10000)</f>
         <v/>
       </c>
+      <c r="P104" s="7" t="n"/>
+      <c r="Q104" s="7" t="n"/>
+      <c r="R104" s="3">
+        <f>IF(OR(F104="",F104=0),"",(N(P104)+N(H104)+N(Q104)+N(I104))/F104*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -5031,6 +5731,12 @@
         <f>IF(OR(M105="",F105=0),"",M105/F105*10000)</f>
         <v/>
       </c>
+      <c r="P105" s="7" t="n"/>
+      <c r="Q105" s="7" t="n"/>
+      <c r="R105" s="3">
+        <f>IF(OR(F105="",F105=0),"",(N(P105)+N(H105)+N(Q105)+N(I105))/F105*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -5063,6 +5769,12 @@
         <f>IF(OR(M106="",F106=0),"",M106/F106*10000)</f>
         <v/>
       </c>
+      <c r="P106" s="7" t="n"/>
+      <c r="Q106" s="7" t="n"/>
+      <c r="R106" s="3">
+        <f>IF(OR(F106="",F106=0),"",(N(P106)+N(H106)+N(Q106)+N(I106))/F106*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -5095,6 +5807,12 @@
         <f>IF(OR(M107="",F107=0),"",M107/F107*10000)</f>
         <v/>
       </c>
+      <c r="P107" s="7" t="n"/>
+      <c r="Q107" s="7" t="n"/>
+      <c r="R107" s="3">
+        <f>IF(OR(F107="",F107=0),"",(N(P107)+N(H107)+N(Q107)+N(I107))/F107*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -5127,6 +5845,12 @@
         <f>IF(OR(M108="",F108=0),"",M108/F108*10000)</f>
         <v/>
       </c>
+      <c r="P108" s="7" t="n"/>
+      <c r="Q108" s="7" t="n"/>
+      <c r="R108" s="3">
+        <f>IF(OR(F108="",F108=0),"",(N(P108)+N(H108)+N(Q108)+N(I108))/F108*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -5159,6 +5883,12 @@
         <f>IF(OR(M109="",F109=0),"",M109/F109*10000)</f>
         <v/>
       </c>
+      <c r="P109" s="7" t="n"/>
+      <c r="Q109" s="7" t="n"/>
+      <c r="R109" s="3">
+        <f>IF(OR(F109="",F109=0),"",(N(P109)+N(H109)+N(Q109)+N(I109))/F109*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -5191,6 +5921,12 @@
         <f>IF(OR(M110="",F110=0),"",M110/F110*10000)</f>
         <v/>
       </c>
+      <c r="P110" s="7" t="n"/>
+      <c r="Q110" s="7" t="n"/>
+      <c r="R110" s="3">
+        <f>IF(OR(F110="",F110=0),"",(N(P110)+N(H110)+N(Q110)+N(I110))/F110*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -5223,6 +5959,12 @@
         <f>IF(OR(M111="",F111=0),"",M111/F111*10000)</f>
         <v/>
       </c>
+      <c r="P111" s="7" t="n"/>
+      <c r="Q111" s="7" t="n"/>
+      <c r="R111" s="3">
+        <f>IF(OR(F111="",F111=0),"",(N(P111)+N(H111)+N(Q111)+N(I111))/F111*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -5255,6 +5997,12 @@
         <f>IF(OR(M112="",F112=0),"",M112/F112*10000)</f>
         <v/>
       </c>
+      <c r="P112" s="7" t="n"/>
+      <c r="Q112" s="7" t="n"/>
+      <c r="R112" s="3">
+        <f>IF(OR(F112="",F112=0),"",(N(P112)+N(H112)+N(Q112)+N(I112))/F112*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -5287,6 +6035,12 @@
         <f>IF(OR(M113="",F113=0),"",M113/F113*10000)</f>
         <v/>
       </c>
+      <c r="P113" s="7" t="n"/>
+      <c r="Q113" s="7" t="n"/>
+      <c r="R113" s="3">
+        <f>IF(OR(F113="",F113=0),"",(N(P113)+N(H113)+N(Q113)+N(I113))/F113*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -5319,6 +6073,12 @@
         <f>IF(OR(M114="",F114=0),"",M114/F114*10000)</f>
         <v/>
       </c>
+      <c r="P114" s="7" t="n"/>
+      <c r="Q114" s="7" t="n"/>
+      <c r="R114" s="3">
+        <f>IF(OR(F114="",F114=0),"",(N(P114)+N(H114)+N(Q114)+N(I114))/F114*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -5351,6 +6111,12 @@
         <f>IF(OR(M115="",F115=0),"",M115/F115*10000)</f>
         <v/>
       </c>
+      <c r="P115" s="7" t="n"/>
+      <c r="Q115" s="7" t="n"/>
+      <c r="R115" s="3">
+        <f>IF(OR(F115="",F115=0),"",(N(P115)+N(H115)+N(Q115)+N(I115))/F115*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -5383,6 +6149,12 @@
         <f>IF(OR(M116="",F116=0),"",M116/F116*10000)</f>
         <v/>
       </c>
+      <c r="P116" s="7" t="n"/>
+      <c r="Q116" s="7" t="n"/>
+      <c r="R116" s="3">
+        <f>IF(OR(F116="",F116=0),"",(N(P116)+N(H116)+N(Q116)+N(I116))/F116*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -5415,6 +6187,12 @@
         <f>IF(OR(M117="",F117=0),"",M117/F117*10000)</f>
         <v/>
       </c>
+      <c r="P117" s="7" t="n"/>
+      <c r="Q117" s="7" t="n"/>
+      <c r="R117" s="3">
+        <f>IF(OR(F117="",F117=0),"",(N(P117)+N(H117)+N(Q117)+N(I117))/F117*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -5447,6 +6225,12 @@
         <f>IF(OR(M118="",F118=0),"",M118/F118*10000)</f>
         <v/>
       </c>
+      <c r="P118" s="7" t="n"/>
+      <c r="Q118" s="7" t="n"/>
+      <c r="R118" s="3">
+        <f>IF(OR(F118="",F118=0),"",(N(P118)+N(H118)+N(Q118)+N(I118))/F118*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -5479,6 +6263,12 @@
         <f>IF(OR(M119="",F119=0),"",M119/F119*10000)</f>
         <v/>
       </c>
+      <c r="P119" s="7" t="n"/>
+      <c r="Q119" s="7" t="n"/>
+      <c r="R119" s="3">
+        <f>IF(OR(F119="",F119=0),"",(N(P119)+N(H119)+N(Q119)+N(I119))/F119*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -5511,6 +6301,12 @@
         <f>IF(OR(M120="",F120=0),"",M120/F120*10000)</f>
         <v/>
       </c>
+      <c r="P120" s="7" t="n"/>
+      <c r="Q120" s="7" t="n"/>
+      <c r="R120" s="3">
+        <f>IF(OR(F120="",F120=0),"",(N(P120)+N(H120)+N(Q120)+N(I120))/F120*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -5543,6 +6339,12 @@
         <f>IF(OR(M121="",F121=0),"",M121/F121*10000)</f>
         <v/>
       </c>
+      <c r="P121" s="7" t="n"/>
+      <c r="Q121" s="7" t="n"/>
+      <c r="R121" s="3">
+        <f>IF(OR(F121="",F121=0),"",(N(P121)+N(H121)+N(Q121)+N(I121))/F121*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -5575,6 +6377,12 @@
         <f>IF(OR(M122="",F122=0),"",M122/F122*10000)</f>
         <v/>
       </c>
+      <c r="P122" s="7" t="n"/>
+      <c r="Q122" s="7" t="n"/>
+      <c r="R122" s="3">
+        <f>IF(OR(F122="",F122=0),"",(N(P122)+N(H122)+N(Q122)+N(I122))/F122*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -5607,6 +6415,12 @@
         <f>IF(OR(M123="",F123=0),"",M123/F123*10000)</f>
         <v/>
       </c>
+      <c r="P123" s="7" t="n"/>
+      <c r="Q123" s="7" t="n"/>
+      <c r="R123" s="3">
+        <f>IF(OR(F123="",F123=0),"",(N(P123)+N(H123)+N(Q123)+N(I123))/F123*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -5639,6 +6453,12 @@
         <f>IF(OR(M124="",F124=0),"",M124/F124*10000)</f>
         <v/>
       </c>
+      <c r="P124" s="7" t="n"/>
+      <c r="Q124" s="7" t="n"/>
+      <c r="R124" s="3">
+        <f>IF(OR(F124="",F124=0),"",(N(P124)+N(H124)+N(Q124)+N(I124))/F124*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -5671,6 +6491,12 @@
         <f>IF(OR(M125="",F125=0),"",M125/F125*10000)</f>
         <v/>
       </c>
+      <c r="P125" s="7" t="n"/>
+      <c r="Q125" s="7" t="n"/>
+      <c r="R125" s="3">
+        <f>IF(OR(F125="",F125=0),"",(N(P125)+N(H125)+N(Q125)+N(I125))/F125*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -5703,6 +6529,12 @@
         <f>IF(OR(M126="",F126=0),"",M126/F126*10000)</f>
         <v/>
       </c>
+      <c r="P126" s="7" t="n"/>
+      <c r="Q126" s="7" t="n"/>
+      <c r="R126" s="3">
+        <f>IF(OR(F126="",F126=0),"",(N(P126)+N(H126)+N(Q126)+N(I126))/F126*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -5735,6 +6567,12 @@
         <f>IF(OR(M127="",F127=0),"",M127/F127*10000)</f>
         <v/>
       </c>
+      <c r="P127" s="7" t="n"/>
+      <c r="Q127" s="7" t="n"/>
+      <c r="R127" s="3">
+        <f>IF(OR(F127="",F127=0),"",(N(P127)+N(H127)+N(Q127)+N(I127))/F127*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -5767,6 +6605,12 @@
         <f>IF(OR(M128="",F128=0),"",M128/F128*10000)</f>
         <v/>
       </c>
+      <c r="P128" s="7" t="n"/>
+      <c r="Q128" s="7" t="n"/>
+      <c r="R128" s="3">
+        <f>IF(OR(F128="",F128=0),"",(N(P128)+N(H128)+N(Q128)+N(I128))/F128*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -5799,6 +6643,12 @@
         <f>IF(OR(M129="",F129=0),"",M129/F129*10000)</f>
         <v/>
       </c>
+      <c r="P129" s="7" t="n"/>
+      <c r="Q129" s="7" t="n"/>
+      <c r="R129" s="3">
+        <f>IF(OR(F129="",F129=0),"",(N(P129)+N(H129)+N(Q129)+N(I129))/F129*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -5831,6 +6681,12 @@
         <f>IF(OR(M130="",F130=0),"",M130/F130*10000)</f>
         <v/>
       </c>
+      <c r="P130" s="7" t="n"/>
+      <c r="Q130" s="7" t="n"/>
+      <c r="R130" s="3">
+        <f>IF(OR(F130="",F130=0),"",(N(P130)+N(H130)+N(Q130)+N(I130))/F130*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -5863,6 +6719,12 @@
         <f>IF(OR(M131="",F131=0),"",M131/F131*10000)</f>
         <v/>
       </c>
+      <c r="P131" s="7" t="n"/>
+      <c r="Q131" s="7" t="n"/>
+      <c r="R131" s="3">
+        <f>IF(OR(F131="",F131=0),"",(N(P131)+N(H131)+N(Q131)+N(I131))/F131*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -5895,6 +6757,12 @@
         <f>IF(OR(M132="",F132=0),"",M132/F132*10000)</f>
         <v/>
       </c>
+      <c r="P132" s="7" t="n"/>
+      <c r="Q132" s="7" t="n"/>
+      <c r="R132" s="3">
+        <f>IF(OR(F132="",F132=0),"",(N(P132)+N(H132)+N(Q132)+N(I132))/F132*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -5927,6 +6795,12 @@
         <f>IF(OR(M133="",F133=0),"",M133/F133*10000)</f>
         <v/>
       </c>
+      <c r="P133" s="7" t="n"/>
+      <c r="Q133" s="7" t="n"/>
+      <c r="R133" s="3">
+        <f>IF(OR(F133="",F133=0),"",(N(P133)+N(H133)+N(Q133)+N(I133))/F133*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -5959,6 +6833,12 @@
         <f>IF(OR(M134="",F134=0),"",M134/F134*10000)</f>
         <v/>
       </c>
+      <c r="P134" s="7" t="n"/>
+      <c r="Q134" s="7" t="n"/>
+      <c r="R134" s="3">
+        <f>IF(OR(F134="",F134=0),"",(N(P134)+N(H134)+N(Q134)+N(I134))/F134*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -5991,6 +6871,12 @@
         <f>IF(OR(M135="",F135=0),"",M135/F135*10000)</f>
         <v/>
       </c>
+      <c r="P135" s="7" t="n"/>
+      <c r="Q135" s="7" t="n"/>
+      <c r="R135" s="3">
+        <f>IF(OR(F135="",F135=0),"",(N(P135)+N(H135)+N(Q135)+N(I135))/F135*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -6023,6 +6909,12 @@
         <f>IF(OR(M136="",F136=0),"",M136/F136*10000)</f>
         <v/>
       </c>
+      <c r="P136" s="7" t="n"/>
+      <c r="Q136" s="7" t="n"/>
+      <c r="R136" s="3">
+        <f>IF(OR(F136="",F136=0),"",(N(P136)+N(H136)+N(Q136)+N(I136))/F136*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -6055,6 +6947,12 @@
         <f>IF(OR(M137="",F137=0),"",M137/F137*10000)</f>
         <v/>
       </c>
+      <c r="P137" s="7" t="n"/>
+      <c r="Q137" s="7" t="n"/>
+      <c r="R137" s="3">
+        <f>IF(OR(F137="",F137=0),"",(N(P137)+N(H137)+N(Q137)+N(I137))/F137*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -6087,6 +6985,12 @@
         <f>IF(OR(M138="",F138=0),"",M138/F138*10000)</f>
         <v/>
       </c>
+      <c r="P138" s="7" t="n"/>
+      <c r="Q138" s="7" t="n"/>
+      <c r="R138" s="3">
+        <f>IF(OR(F138="",F138=0),"",(N(P138)+N(H138)+N(Q138)+N(I138))/F138*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -6119,6 +7023,12 @@
         <f>IF(OR(M139="",F139=0),"",M139/F139*10000)</f>
         <v/>
       </c>
+      <c r="P139" s="7" t="n"/>
+      <c r="Q139" s="7" t="n"/>
+      <c r="R139" s="3">
+        <f>IF(OR(F139="",F139=0),"",(N(P139)+N(H139)+N(Q139)+N(I139))/F139*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -6151,6 +7061,12 @@
         <f>IF(OR(M140="",F140=0),"",M140/F140*10000)</f>
         <v/>
       </c>
+      <c r="P140" s="7" t="n"/>
+      <c r="Q140" s="7" t="n"/>
+      <c r="R140" s="3">
+        <f>IF(OR(F140="",F140=0),"",(N(P140)+N(H140)+N(Q140)+N(I140))/F140*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -6183,6 +7099,12 @@
         <f>IF(OR(M141="",F141=0),"",M141/F141*10000)</f>
         <v/>
       </c>
+      <c r="P141" s="7" t="n"/>
+      <c r="Q141" s="7" t="n"/>
+      <c r="R141" s="3">
+        <f>IF(OR(F141="",F141=0),"",(N(P141)+N(H141)+N(Q141)+N(I141))/F141*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -6215,6 +7137,12 @@
         <f>IF(OR(M142="",F142=0),"",M142/F142*10000)</f>
         <v/>
       </c>
+      <c r="P142" s="7" t="n"/>
+      <c r="Q142" s="7" t="n"/>
+      <c r="R142" s="3">
+        <f>IF(OR(F142="",F142=0),"",(N(P142)+N(H142)+N(Q142)+N(I142))/F142*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -6247,6 +7175,12 @@
         <f>IF(OR(M143="",F143=0),"",M143/F143*10000)</f>
         <v/>
       </c>
+      <c r="P143" s="7" t="n"/>
+      <c r="Q143" s="7" t="n"/>
+      <c r="R143" s="3">
+        <f>IF(OR(F143="",F143=0),"",(N(P143)+N(H143)+N(Q143)+N(I143))/F143*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -6279,6 +7213,12 @@
         <f>IF(OR(M144="",F144=0),"",M144/F144*10000)</f>
         <v/>
       </c>
+      <c r="P144" s="7" t="n"/>
+      <c r="Q144" s="7" t="n"/>
+      <c r="R144" s="3">
+        <f>IF(OR(F144="",F144=0),"",(N(P144)+N(H144)+N(Q144)+N(I144))/F144*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -6311,6 +7251,12 @@
         <f>IF(OR(M145="",F145=0),"",M145/F145*10000)</f>
         <v/>
       </c>
+      <c r="P145" s="7" t="n"/>
+      <c r="Q145" s="7" t="n"/>
+      <c r="R145" s="3">
+        <f>IF(OR(F145="",F145=0),"",(N(P145)+N(H145)+N(Q145)+N(I145))/F145*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -6343,6 +7289,12 @@
         <f>IF(OR(M146="",F146=0),"",M146/F146*10000)</f>
         <v/>
       </c>
+      <c r="P146" s="7" t="n"/>
+      <c r="Q146" s="7" t="n"/>
+      <c r="R146" s="3">
+        <f>IF(OR(F146="",F146=0),"",(N(P146)+N(H146)+N(Q146)+N(I146))/F146*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -6375,6 +7327,12 @@
         <f>IF(OR(M147="",F147=0),"",M147/F147*10000)</f>
         <v/>
       </c>
+      <c r="P147" s="7" t="n"/>
+      <c r="Q147" s="7" t="n"/>
+      <c r="R147" s="3">
+        <f>IF(OR(F147="",F147=0),"",(N(P147)+N(H147)+N(Q147)+N(I147))/F147*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -6407,6 +7365,12 @@
         <f>IF(OR(M148="",F148=0),"",M148/F148*10000)</f>
         <v/>
       </c>
+      <c r="P148" s="7" t="n"/>
+      <c r="Q148" s="7" t="n"/>
+      <c r="R148" s="3">
+        <f>IF(OR(F148="",F148=0),"",(N(P148)+N(H148)+N(Q148)+N(I148))/F148*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -6439,6 +7403,12 @@
         <f>IF(OR(M149="",F149=0),"",M149/F149*10000)</f>
         <v/>
       </c>
+      <c r="P149" s="7" t="n"/>
+      <c r="Q149" s="7" t="n"/>
+      <c r="R149" s="3">
+        <f>IF(OR(F149="",F149=0),"",(N(P149)+N(H149)+N(Q149)+N(I149))/F149*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -6471,6 +7441,12 @@
         <f>IF(OR(M150="",F150=0),"",M150/F150*10000)</f>
         <v/>
       </c>
+      <c r="P150" s="7" t="n"/>
+      <c r="Q150" s="7" t="n"/>
+      <c r="R150" s="3">
+        <f>IF(OR(F150="",F150=0),"",(N(P150)+N(H150)+N(Q150)+N(I150))/F150*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -6503,6 +7479,12 @@
         <f>IF(OR(M151="",F151=0),"",M151/F151*10000)</f>
         <v/>
       </c>
+      <c r="P151" s="7" t="n"/>
+      <c r="Q151" s="7" t="n"/>
+      <c r="R151" s="3">
+        <f>IF(OR(F151="",F151=0),"",(N(P151)+N(H151)+N(Q151)+N(I151))/F151*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -6535,6 +7517,12 @@
         <f>IF(OR(M152="",F152=0),"",M152/F152*10000)</f>
         <v/>
       </c>
+      <c r="P152" s="7" t="n"/>
+      <c r="Q152" s="7" t="n"/>
+      <c r="R152" s="3">
+        <f>IF(OR(F152="",F152=0),"",(N(P152)+N(H152)+N(Q152)+N(I152))/F152*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -6567,6 +7555,12 @@
         <f>IF(OR(M153="",F153=0),"",M153/F153*10000)</f>
         <v/>
       </c>
+      <c r="P153" s="7" t="n"/>
+      <c r="Q153" s="7" t="n"/>
+      <c r="R153" s="3">
+        <f>IF(OR(F153="",F153=0),"",(N(P153)+N(H153)+N(Q153)+N(I153))/F153*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -6599,6 +7593,12 @@
         <f>IF(OR(M154="",F154=0),"",M154/F154*10000)</f>
         <v/>
       </c>
+      <c r="P154" s="7" t="n"/>
+      <c r="Q154" s="7" t="n"/>
+      <c r="R154" s="3">
+        <f>IF(OR(F154="",F154=0),"",(N(P154)+N(H154)+N(Q154)+N(I154))/F154*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -6631,6 +7631,12 @@
         <f>IF(OR(M155="",F155=0),"",M155/F155*10000)</f>
         <v/>
       </c>
+      <c r="P155" s="7" t="n"/>
+      <c r="Q155" s="7" t="n"/>
+      <c r="R155" s="3">
+        <f>IF(OR(F155="",F155=0),"",(N(P155)+N(H155)+N(Q155)+N(I155))/F155*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -6663,6 +7669,12 @@
         <f>IF(OR(M156="",F156=0),"",M156/F156*10000)</f>
         <v/>
       </c>
+      <c r="P156" s="7" t="n"/>
+      <c r="Q156" s="7" t="n"/>
+      <c r="R156" s="3">
+        <f>IF(OR(F156="",F156=0),"",(N(P156)+N(H156)+N(Q156)+N(I156))/F156*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -6695,6 +7707,12 @@
         <f>IF(OR(M157="",F157=0),"",M157/F157*10000)</f>
         <v/>
       </c>
+      <c r="P157" s="7" t="n"/>
+      <c r="Q157" s="7" t="n"/>
+      <c r="R157" s="3">
+        <f>IF(OR(F157="",F157=0),"",(N(P157)+N(H157)+N(Q157)+N(I157))/F157*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -6727,6 +7745,12 @@
         <f>IF(OR(M158="",F158=0),"",M158/F158*10000)</f>
         <v/>
       </c>
+      <c r="P158" s="7" t="n"/>
+      <c r="Q158" s="7" t="n"/>
+      <c r="R158" s="3">
+        <f>IF(OR(F158="",F158=0),"",(N(P158)+N(H158)+N(Q158)+N(I158))/F158*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -6759,6 +7783,12 @@
         <f>IF(OR(M159="",F159=0),"",M159/F159*10000)</f>
         <v/>
       </c>
+      <c r="P159" s="7" t="n"/>
+      <c r="Q159" s="7" t="n"/>
+      <c r="R159" s="3">
+        <f>IF(OR(F159="",F159=0),"",(N(P159)+N(H159)+N(Q159)+N(I159))/F159*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -6791,6 +7821,12 @@
         <f>IF(OR(M160="",F160=0),"",M160/F160*10000)</f>
         <v/>
       </c>
+      <c r="P160" s="7" t="n"/>
+      <c r="Q160" s="7" t="n"/>
+      <c r="R160" s="3">
+        <f>IF(OR(F160="",F160=0),"",(N(P160)+N(H160)+N(Q160)+N(I160))/F160*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -6823,6 +7859,12 @@
         <f>IF(OR(M161="",F161=0),"",M161/F161*10000)</f>
         <v/>
       </c>
+      <c r="P161" s="7" t="n"/>
+      <c r="Q161" s="7" t="n"/>
+      <c r="R161" s="3">
+        <f>IF(OR(F161="",F161=0),"",(N(P161)+N(H161)+N(Q161)+N(I161))/F161*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -6855,6 +7897,12 @@
         <f>IF(OR(M162="",F162=0),"",M162/F162*10000)</f>
         <v/>
       </c>
+      <c r="P162" s="7" t="n"/>
+      <c r="Q162" s="7" t="n"/>
+      <c r="R162" s="3">
+        <f>IF(OR(F162="",F162=0),"",(N(P162)+N(H162)+N(Q162)+N(I162))/F162*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -6887,6 +7935,12 @@
         <f>IF(OR(M163="",F163=0),"",M163/F163*10000)</f>
         <v/>
       </c>
+      <c r="P163" s="7" t="n"/>
+      <c r="Q163" s="7" t="n"/>
+      <c r="R163" s="3">
+        <f>IF(OR(F163="",F163=0),"",(N(P163)+N(H163)+N(Q163)+N(I163))/F163*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -6919,6 +7973,12 @@
         <f>IF(OR(M164="",F164=0),"",M164/F164*10000)</f>
         <v/>
       </c>
+      <c r="P164" s="7" t="n"/>
+      <c r="Q164" s="7" t="n"/>
+      <c r="R164" s="3">
+        <f>IF(OR(F164="",F164=0),"",(N(P164)+N(H164)+N(Q164)+N(I164))/F164*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -6951,6 +8011,12 @@
         <f>IF(OR(M165="",F165=0),"",M165/F165*10000)</f>
         <v/>
       </c>
+      <c r="P165" s="7" t="n"/>
+      <c r="Q165" s="7" t="n"/>
+      <c r="R165" s="3">
+        <f>IF(OR(F165="",F165=0),"",(N(P165)+N(H165)+N(Q165)+N(I165))/F165*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -6983,6 +8049,12 @@
         <f>IF(OR(M166="",F166=0),"",M166/F166*10000)</f>
         <v/>
       </c>
+      <c r="P166" s="7" t="n"/>
+      <c r="Q166" s="7" t="n"/>
+      <c r="R166" s="3">
+        <f>IF(OR(F166="",F166=0),"",(N(P166)+N(H166)+N(Q166)+N(I166))/F166*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -7015,6 +8087,12 @@
         <f>IF(OR(M167="",F167=0),"",M167/F167*10000)</f>
         <v/>
       </c>
+      <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="n"/>
+      <c r="R167" s="3">
+        <f>IF(OR(F167="",F167=0),"",(N(P167)+N(H167)+N(Q167)+N(I167))/F167*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -7047,6 +8125,12 @@
         <f>IF(OR(M168="",F168=0),"",M168/F168*10000)</f>
         <v/>
       </c>
+      <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="n"/>
+      <c r="R168" s="3">
+        <f>IF(OR(F168="",F168=0),"",(N(P168)+N(H168)+N(Q168)+N(I168))/F168*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -7079,6 +8163,12 @@
         <f>IF(OR(M169="",F169=0),"",M169/F169*10000)</f>
         <v/>
       </c>
+      <c r="P169" s="7" t="n"/>
+      <c r="Q169" s="7" t="n"/>
+      <c r="R169" s="3">
+        <f>IF(OR(F169="",F169=0),"",(N(P169)+N(H169)+N(Q169)+N(I169))/F169*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -7111,6 +8201,12 @@
         <f>IF(OR(M170="",F170=0),"",M170/F170*10000)</f>
         <v/>
       </c>
+      <c r="P170" s="7" t="n"/>
+      <c r="Q170" s="7" t="n"/>
+      <c r="R170" s="3">
+        <f>IF(OR(F170="",F170=0),"",(N(P170)+N(H170)+N(Q170)+N(I170))/F170*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -7143,6 +8239,12 @@
         <f>IF(OR(M171="",F171=0),"",M171/F171*10000)</f>
         <v/>
       </c>
+      <c r="P171" s="7" t="n"/>
+      <c r="Q171" s="7" t="n"/>
+      <c r="R171" s="3">
+        <f>IF(OR(F171="",F171=0),"",(N(P171)+N(H171)+N(Q171)+N(I171))/F171*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -7175,6 +8277,12 @@
         <f>IF(OR(M172="",F172=0),"",M172/F172*10000)</f>
         <v/>
       </c>
+      <c r="P172" s="7" t="n"/>
+      <c r="Q172" s="7" t="n"/>
+      <c r="R172" s="3">
+        <f>IF(OR(F172="",F172=0),"",(N(P172)+N(H172)+N(Q172)+N(I172))/F172*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -7207,6 +8315,12 @@
         <f>IF(OR(M173="",F173=0),"",M173/F173*10000)</f>
         <v/>
       </c>
+      <c r="P173" s="7" t="n"/>
+      <c r="Q173" s="7" t="n"/>
+      <c r="R173" s="3">
+        <f>IF(OR(F173="",F173=0),"",(N(P173)+N(H173)+N(Q173)+N(I173))/F173*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -7239,6 +8353,12 @@
         <f>IF(OR(M174="",F174=0),"",M174/F174*10000)</f>
         <v/>
       </c>
+      <c r="P174" s="7" t="n"/>
+      <c r="Q174" s="7" t="n"/>
+      <c r="R174" s="3">
+        <f>IF(OR(F174="",F174=0),"",(N(P174)+N(H174)+N(Q174)+N(I174))/F174*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -7271,6 +8391,12 @@
         <f>IF(OR(M175="",F175=0),"",M175/F175*10000)</f>
         <v/>
       </c>
+      <c r="P175" s="7" t="n"/>
+      <c r="Q175" s="7" t="n"/>
+      <c r="R175" s="3">
+        <f>IF(OR(F175="",F175=0),"",(N(P175)+N(H175)+N(Q175)+N(I175))/F175*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -7303,6 +8429,12 @@
         <f>IF(OR(M176="",F176=0),"",M176/F176*10000)</f>
         <v/>
       </c>
+      <c r="P176" s="7" t="n"/>
+      <c r="Q176" s="7" t="n"/>
+      <c r="R176" s="3">
+        <f>IF(OR(F176="",F176=0),"",(N(P176)+N(H176)+N(Q176)+N(I176))/F176*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -7335,6 +8467,12 @@
         <f>IF(OR(M177="",F177=0),"",M177/F177*10000)</f>
         <v/>
       </c>
+      <c r="P177" s="7" t="n"/>
+      <c r="Q177" s="7" t="n"/>
+      <c r="R177" s="3">
+        <f>IF(OR(F177="",F177=0),"",(N(P177)+N(H177)+N(Q177)+N(I177))/F177*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -7367,6 +8505,12 @@
         <f>IF(OR(M178="",F178=0),"",M178/F178*10000)</f>
         <v/>
       </c>
+      <c r="P178" s="7" t="n"/>
+      <c r="Q178" s="7" t="n"/>
+      <c r="R178" s="3">
+        <f>IF(OR(F178="",F178=0),"",(N(P178)+N(H178)+N(Q178)+N(I178))/F178*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -7399,6 +8543,12 @@
         <f>IF(OR(M179="",F179=0),"",M179/F179*10000)</f>
         <v/>
       </c>
+      <c r="P179" s="7" t="n"/>
+      <c r="Q179" s="7" t="n"/>
+      <c r="R179" s="3">
+        <f>IF(OR(F179="",F179=0),"",(N(P179)+N(H179)+N(Q179)+N(I179))/F179*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -7431,6 +8581,12 @@
         <f>IF(OR(M180="",F180=0),"",M180/F180*10000)</f>
         <v/>
       </c>
+      <c r="P180" s="7" t="n"/>
+      <c r="Q180" s="7" t="n"/>
+      <c r="R180" s="3">
+        <f>IF(OR(F180="",F180=0),"",(N(P180)+N(H180)+N(Q180)+N(I180))/F180*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -7463,6 +8619,12 @@
         <f>IF(OR(M181="",F181=0),"",M181/F181*10000)</f>
         <v/>
       </c>
+      <c r="P181" s="7" t="n"/>
+      <c r="Q181" s="7" t="n"/>
+      <c r="R181" s="3">
+        <f>IF(OR(F181="",F181=0),"",(N(P181)+N(H181)+N(Q181)+N(I181))/F181*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -7495,6 +8657,12 @@
         <f>IF(OR(M182="",F182=0),"",M182/F182*10000)</f>
         <v/>
       </c>
+      <c r="P182" s="7" t="n"/>
+      <c r="Q182" s="7" t="n"/>
+      <c r="R182" s="3">
+        <f>IF(OR(F182="",F182=0),"",(N(P182)+N(H182)+N(Q182)+N(I182))/F182*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -7527,6 +8695,12 @@
         <f>IF(OR(M183="",F183=0),"",M183/F183*10000)</f>
         <v/>
       </c>
+      <c r="P183" s="7" t="n"/>
+      <c r="Q183" s="7" t="n"/>
+      <c r="R183" s="3">
+        <f>IF(OR(F183="",F183=0),"",(N(P183)+N(H183)+N(Q183)+N(I183))/F183*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -7559,6 +8733,12 @@
         <f>IF(OR(M184="",F184=0),"",M184/F184*10000)</f>
         <v/>
       </c>
+      <c r="P184" s="7" t="n"/>
+      <c r="Q184" s="7" t="n"/>
+      <c r="R184" s="3">
+        <f>IF(OR(F184="",F184=0),"",(N(P184)+N(H184)+N(Q184)+N(I184))/F184*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -7591,6 +8771,12 @@
         <f>IF(OR(M185="",F185=0),"",M185/F185*10000)</f>
         <v/>
       </c>
+      <c r="P185" s="7" t="n"/>
+      <c r="Q185" s="7" t="n"/>
+      <c r="R185" s="3">
+        <f>IF(OR(F185="",F185=0),"",(N(P185)+N(H185)+N(Q185)+N(I185))/F185*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -7623,6 +8809,12 @@
         <f>IF(OR(M186="",F186=0),"",M186/F186*10000)</f>
         <v/>
       </c>
+      <c r="P186" s="7" t="n"/>
+      <c r="Q186" s="7" t="n"/>
+      <c r="R186" s="3">
+        <f>IF(OR(F186="",F186=0),"",(N(P186)+N(H186)+N(Q186)+N(I186))/F186*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -7655,6 +8847,12 @@
         <f>IF(OR(M187="",F187=0),"",M187/F187*10000)</f>
         <v/>
       </c>
+      <c r="P187" s="7" t="n"/>
+      <c r="Q187" s="7" t="n"/>
+      <c r="R187" s="3">
+        <f>IF(OR(F187="",F187=0),"",(N(P187)+N(H187)+N(Q187)+N(I187))/F187*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -7687,6 +8885,12 @@
         <f>IF(OR(M188="",F188=0),"",M188/F188*10000)</f>
         <v/>
       </c>
+      <c r="P188" s="7" t="n"/>
+      <c r="Q188" s="7" t="n"/>
+      <c r="R188" s="3">
+        <f>IF(OR(F188="",F188=0),"",(N(P188)+N(H188)+N(Q188)+N(I188))/F188*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -7719,6 +8923,12 @@
         <f>IF(OR(M189="",F189=0),"",M189/F189*10000)</f>
         <v/>
       </c>
+      <c r="P189" s="7" t="n"/>
+      <c r="Q189" s="7" t="n"/>
+      <c r="R189" s="3">
+        <f>IF(OR(F189="",F189=0),"",(N(P189)+N(H189)+N(Q189)+N(I189))/F189*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -7751,6 +8961,12 @@
         <f>IF(OR(M190="",F190=0),"",M190/F190*10000)</f>
         <v/>
       </c>
+      <c r="P190" s="7" t="n"/>
+      <c r="Q190" s="7" t="n"/>
+      <c r="R190" s="3">
+        <f>IF(OR(F190="",F190=0),"",(N(P190)+N(H190)+N(Q190)+N(I190))/F190*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -7783,6 +8999,12 @@
         <f>IF(OR(M191="",F191=0),"",M191/F191*10000)</f>
         <v/>
       </c>
+      <c r="P191" s="7" t="n"/>
+      <c r="Q191" s="7" t="n"/>
+      <c r="R191" s="3">
+        <f>IF(OR(F191="",F191=0),"",(N(P191)+N(H191)+N(Q191)+N(I191))/F191*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -7815,6 +9037,12 @@
         <f>IF(OR(M192="",F192=0),"",M192/F192*10000)</f>
         <v/>
       </c>
+      <c r="P192" s="7" t="n"/>
+      <c r="Q192" s="7" t="n"/>
+      <c r="R192" s="3">
+        <f>IF(OR(F192="",F192=0),"",(N(P192)+N(H192)+N(Q192)+N(I192))/F192*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -7847,6 +9075,12 @@
         <f>IF(OR(M193="",F193=0),"",M193/F193*10000)</f>
         <v/>
       </c>
+      <c r="P193" s="7" t="n"/>
+      <c r="Q193" s="7" t="n"/>
+      <c r="R193" s="3">
+        <f>IF(OR(F193="",F193=0),"",(N(P193)+N(H193)+N(Q193)+N(I193))/F193*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -7879,6 +9113,12 @@
         <f>IF(OR(M194="",F194=0),"",M194/F194*10000)</f>
         <v/>
       </c>
+      <c r="P194" s="7" t="n"/>
+      <c r="Q194" s="7" t="n"/>
+      <c r="R194" s="3">
+        <f>IF(OR(F194="",F194=0),"",(N(P194)+N(H194)+N(Q194)+N(I194))/F194*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -7911,6 +9151,12 @@
         <f>IF(OR(M195="",F195=0),"",M195/F195*10000)</f>
         <v/>
       </c>
+      <c r="P195" s="7" t="n"/>
+      <c r="Q195" s="7" t="n"/>
+      <c r="R195" s="3">
+        <f>IF(OR(F195="",F195=0),"",(N(P195)+N(H195)+N(Q195)+N(I195))/F195*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -7943,6 +9189,12 @@
         <f>IF(OR(M196="",F196=0),"",M196/F196*10000)</f>
         <v/>
       </c>
+      <c r="P196" s="7" t="n"/>
+      <c r="Q196" s="7" t="n"/>
+      <c r="R196" s="3">
+        <f>IF(OR(F196="",F196=0),"",(N(P196)+N(H196)+N(Q196)+N(I196))/F196*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -7975,6 +9227,12 @@
         <f>IF(OR(M197="",F197=0),"",M197/F197*10000)</f>
         <v/>
       </c>
+      <c r="P197" s="7" t="n"/>
+      <c r="Q197" s="7" t="n"/>
+      <c r="R197" s="3">
+        <f>IF(OR(F197="",F197=0),"",(N(P197)+N(H197)+N(Q197)+N(I197))/F197*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -8007,6 +9265,12 @@
         <f>IF(OR(M198="",F198=0),"",M198/F198*10000)</f>
         <v/>
       </c>
+      <c r="P198" s="7" t="n"/>
+      <c r="Q198" s="7" t="n"/>
+      <c r="R198" s="3">
+        <f>IF(OR(F198="",F198=0),"",(N(P198)+N(H198)+N(Q198)+N(I198))/F198*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -8039,6 +9303,12 @@
         <f>IF(OR(M199="",F199=0),"",M199/F199*10000)</f>
         <v/>
       </c>
+      <c r="P199" s="7" t="n"/>
+      <c r="Q199" s="7" t="n"/>
+      <c r="R199" s="3">
+        <f>IF(OR(F199="",F199=0),"",(N(P199)+N(H199)+N(Q199)+N(I199))/F199*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -8071,6 +9341,12 @@
         <f>IF(OR(M200="",F200=0),"",M200/F200*10000)</f>
         <v/>
       </c>
+      <c r="P200" s="7" t="n"/>
+      <c r="Q200" s="7" t="n"/>
+      <c r="R200" s="3">
+        <f>IF(OR(F200="",F200=0),"",(N(P200)+N(H200)+N(Q200)+N(I200))/F200*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -8103,6 +9379,12 @@
         <f>IF(OR(M201="",F201=0),"",M201/F201*10000)</f>
         <v/>
       </c>
+      <c r="P201" s="7" t="n"/>
+      <c r="Q201" s="7" t="n"/>
+      <c r="R201" s="3">
+        <f>IF(OR(F201="",F201=0),"",(N(P201)+N(H201)+N(Q201)+N(I201))/F201*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -8135,6 +9417,12 @@
         <f>IF(OR(M202="",F202=0),"",M202/F202*10000)</f>
         <v/>
       </c>
+      <c r="P202" s="7" t="n"/>
+      <c r="Q202" s="7" t="n"/>
+      <c r="R202" s="3">
+        <f>IF(OR(F202="",F202=0),"",(N(P202)+N(H202)+N(Q202)+N(I202))/F202*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -8167,6 +9455,12 @@
         <f>IF(OR(M203="",F203=0),"",M203/F203*10000)</f>
         <v/>
       </c>
+      <c r="P203" s="7" t="n"/>
+      <c r="Q203" s="7" t="n"/>
+      <c r="R203" s="3">
+        <f>IF(OR(F203="",F203=0),"",(N(P203)+N(H203)+N(Q203)+N(I203))/F203*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -8199,6 +9493,12 @@
         <f>IF(OR(M204="",F204=0),"",M204/F204*10000)</f>
         <v/>
       </c>
+      <c r="P204" s="7" t="n"/>
+      <c r="Q204" s="7" t="n"/>
+      <c r="R204" s="3">
+        <f>IF(OR(F204="",F204=0),"",(N(P204)+N(H204)+N(Q204)+N(I204))/F204*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -8231,6 +9531,12 @@
         <f>IF(OR(M205="",F205=0),"",M205/F205*10000)</f>
         <v/>
       </c>
+      <c r="P205" s="7" t="n"/>
+      <c r="Q205" s="7" t="n"/>
+      <c r="R205" s="3">
+        <f>IF(OR(F205="",F205=0),"",(N(P205)+N(H205)+N(Q205)+N(I205))/F205*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -8263,6 +9569,12 @@
         <f>IF(OR(M206="",F206=0),"",M206/F206*10000)</f>
         <v/>
       </c>
+      <c r="P206" s="7" t="n"/>
+      <c r="Q206" s="7" t="n"/>
+      <c r="R206" s="3">
+        <f>IF(OR(F206="",F206=0),"",(N(P206)+N(H206)+N(Q206)+N(I206))/F206*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -8295,6 +9607,12 @@
         <f>IF(OR(M207="",F207=0),"",M207/F207*10000)</f>
         <v/>
       </c>
+      <c r="P207" s="7" t="n"/>
+      <c r="Q207" s="7" t="n"/>
+      <c r="R207" s="3">
+        <f>IF(OR(F207="",F207=0),"",(N(P207)+N(H207)+N(Q207)+N(I207))/F207*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -8327,6 +9645,12 @@
         <f>IF(OR(M208="",F208=0),"",M208/F208*10000)</f>
         <v/>
       </c>
+      <c r="P208" s="7" t="n"/>
+      <c r="Q208" s="7" t="n"/>
+      <c r="R208" s="3">
+        <f>IF(OR(F208="",F208=0),"",(N(P208)+N(H208)+N(Q208)+N(I208))/F208*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -8359,6 +9683,12 @@
         <f>IF(OR(M209="",F209=0),"",M209/F209*10000)</f>
         <v/>
       </c>
+      <c r="P209" s="7" t="n"/>
+      <c r="Q209" s="7" t="n"/>
+      <c r="R209" s="3">
+        <f>IF(OR(F209="",F209=0),"",(N(P209)+N(H209)+N(Q209)+N(I209))/F209*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -8391,6 +9721,12 @@
         <f>IF(OR(M210="",F210=0),"",M210/F210*10000)</f>
         <v/>
       </c>
+      <c r="P210" s="7" t="n"/>
+      <c r="Q210" s="7" t="n"/>
+      <c r="R210" s="3">
+        <f>IF(OR(F210="",F210=0),"",(N(P210)+N(H210)+N(Q210)+N(I210))/F210*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -8423,6 +9759,12 @@
         <f>IF(OR(M211="",F211=0),"",M211/F211*10000)</f>
         <v/>
       </c>
+      <c r="P211" s="7" t="n"/>
+      <c r="Q211" s="7" t="n"/>
+      <c r="R211" s="3">
+        <f>IF(OR(F211="",F211=0),"",(N(P211)+N(H211)+N(Q211)+N(I211))/F211*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -8455,6 +9797,12 @@
         <f>IF(OR(M212="",F212=0),"",M212/F212*10000)</f>
         <v/>
       </c>
+      <c r="P212" s="7" t="n"/>
+      <c r="Q212" s="7" t="n"/>
+      <c r="R212" s="3">
+        <f>IF(OR(F212="",F212=0),"",(N(P212)+N(H212)+N(Q212)+N(I212))/F212*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -8487,6 +9835,12 @@
         <f>IF(OR(M213="",F213=0),"",M213/F213*10000)</f>
         <v/>
       </c>
+      <c r="P213" s="7" t="n"/>
+      <c r="Q213" s="7" t="n"/>
+      <c r="R213" s="3">
+        <f>IF(OR(F213="",F213=0),"",(N(P213)+N(H213)+N(Q213)+N(I213))/F213*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -8519,6 +9873,12 @@
         <f>IF(OR(M214="",F214=0),"",M214/F214*10000)</f>
         <v/>
       </c>
+      <c r="P214" s="7" t="n"/>
+      <c r="Q214" s="7" t="n"/>
+      <c r="R214" s="3">
+        <f>IF(OR(F214="",F214=0),"",(N(P214)+N(H214)+N(Q214)+N(I214))/F214*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -8551,6 +9911,12 @@
         <f>IF(OR(M215="",F215=0),"",M215/F215*10000)</f>
         <v/>
       </c>
+      <c r="P215" s="7" t="n"/>
+      <c r="Q215" s="7" t="n"/>
+      <c r="R215" s="3">
+        <f>IF(OR(F215="",F215=0),"",(N(P215)+N(H215)+N(Q215)+N(I215))/F215*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -8583,6 +9949,12 @@
         <f>IF(OR(M216="",F216=0),"",M216/F216*10000)</f>
         <v/>
       </c>
+      <c r="P216" s="7" t="n"/>
+      <c r="Q216" s="7" t="n"/>
+      <c r="R216" s="3">
+        <f>IF(OR(F216="",F216=0),"",(N(P216)+N(H216)+N(Q216)+N(I216))/F216*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -8615,6 +9987,12 @@
         <f>IF(OR(M217="",F217=0),"",M217/F217*10000)</f>
         <v/>
       </c>
+      <c r="P217" s="7" t="n"/>
+      <c r="Q217" s="7" t="n"/>
+      <c r="R217" s="3">
+        <f>IF(OR(F217="",F217=0),"",(N(P217)+N(H217)+N(Q217)+N(I217))/F217*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -8647,6 +10025,12 @@
         <f>IF(OR(M218="",F218=0),"",M218/F218*10000)</f>
         <v/>
       </c>
+      <c r="P218" s="7" t="n"/>
+      <c r="Q218" s="7" t="n"/>
+      <c r="R218" s="3">
+        <f>IF(OR(F218="",F218=0),"",(N(P218)+N(H218)+N(Q218)+N(I218))/F218*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -8679,6 +10063,12 @@
         <f>IF(OR(M219="",F219=0),"",M219/F219*10000)</f>
         <v/>
       </c>
+      <c r="P219" s="7" t="n"/>
+      <c r="Q219" s="7" t="n"/>
+      <c r="R219" s="3">
+        <f>IF(OR(F219="",F219=0),"",(N(P219)+N(H219)+N(Q219)+N(I219))/F219*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -8711,6 +10101,12 @@
         <f>IF(OR(M220="",F220=0),"",M220/F220*10000)</f>
         <v/>
       </c>
+      <c r="P220" s="7" t="n"/>
+      <c r="Q220" s="7" t="n"/>
+      <c r="R220" s="3">
+        <f>IF(OR(F220="",F220=0),"",(N(P220)+N(H220)+N(Q220)+N(I220))/F220*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -8743,6 +10139,12 @@
         <f>IF(OR(M221="",F221=0),"",M221/F221*10000)</f>
         <v/>
       </c>
+      <c r="P221" s="7" t="n"/>
+      <c r="Q221" s="7" t="n"/>
+      <c r="R221" s="3">
+        <f>IF(OR(F221="",F221=0),"",(N(P221)+N(H221)+N(Q221)+N(I221))/F221*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -8775,6 +10177,12 @@
         <f>IF(OR(M222="",F222=0),"",M222/F222*10000)</f>
         <v/>
       </c>
+      <c r="P222" s="7" t="n"/>
+      <c r="Q222" s="7" t="n"/>
+      <c r="R222" s="3">
+        <f>IF(OR(F222="",F222=0),"",(N(P222)+N(H222)+N(Q222)+N(I222))/F222*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -8807,6 +10215,12 @@
         <f>IF(OR(M223="",F223=0),"",M223/F223*10000)</f>
         <v/>
       </c>
+      <c r="P223" s="7" t="n"/>
+      <c r="Q223" s="7" t="n"/>
+      <c r="R223" s="3">
+        <f>IF(OR(F223="",F223=0),"",(N(P223)+N(H223)+N(Q223)+N(I223))/F223*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -8839,6 +10253,12 @@
         <f>IF(OR(M224="",F224=0),"",M224/F224*10000)</f>
         <v/>
       </c>
+      <c r="P224" s="7" t="n"/>
+      <c r="Q224" s="7" t="n"/>
+      <c r="R224" s="3">
+        <f>IF(OR(F224="",F224=0),"",(N(P224)+N(H224)+N(Q224)+N(I224))/F224*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -8871,6 +10291,12 @@
         <f>IF(OR(M225="",F225=0),"",M225/F225*10000)</f>
         <v/>
       </c>
+      <c r="P225" s="7" t="n"/>
+      <c r="Q225" s="7" t="n"/>
+      <c r="R225" s="3">
+        <f>IF(OR(F225="",F225=0),"",(N(P225)+N(H225)+N(Q225)+N(I225))/F225*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -8903,6 +10329,12 @@
         <f>IF(OR(M226="",F226=0),"",M226/F226*10000)</f>
         <v/>
       </c>
+      <c r="P226" s="7" t="n"/>
+      <c r="Q226" s="7" t="n"/>
+      <c r="R226" s="3">
+        <f>IF(OR(F226="",F226=0),"",(N(P226)+N(H226)+N(Q226)+N(I226))/F226*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -8935,6 +10367,12 @@
         <f>IF(OR(M227="",F227=0),"",M227/F227*10000)</f>
         <v/>
       </c>
+      <c r="P227" s="7" t="n"/>
+      <c r="Q227" s="7" t="n"/>
+      <c r="R227" s="3">
+        <f>IF(OR(F227="",F227=0),"",(N(P227)+N(H227)+N(Q227)+N(I227))/F227*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -8967,6 +10405,12 @@
         <f>IF(OR(M228="",F228=0),"",M228/F228*10000)</f>
         <v/>
       </c>
+      <c r="P228" s="7" t="n"/>
+      <c r="Q228" s="7" t="n"/>
+      <c r="R228" s="3">
+        <f>IF(OR(F228="",F228=0),"",(N(P228)+N(H228)+N(Q228)+N(I228))/F228*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -8999,6 +10443,12 @@
         <f>IF(OR(M229="",F229=0),"",M229/F229*10000)</f>
         <v/>
       </c>
+      <c r="P229" s="7" t="n"/>
+      <c r="Q229" s="7" t="n"/>
+      <c r="R229" s="3">
+        <f>IF(OR(F229="",F229=0),"",(N(P229)+N(H229)+N(Q229)+N(I229))/F229*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -9031,6 +10481,12 @@
         <f>IF(OR(M230="",F230=0),"",M230/F230*10000)</f>
         <v/>
       </c>
+      <c r="P230" s="7" t="n"/>
+      <c r="Q230" s="7" t="n"/>
+      <c r="R230" s="3">
+        <f>IF(OR(F230="",F230=0),"",(N(P230)+N(H230)+N(Q230)+N(I230))/F230*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -9063,6 +10519,12 @@
         <f>IF(OR(M231="",F231=0),"",M231/F231*10000)</f>
         <v/>
       </c>
+      <c r="P231" s="7" t="n"/>
+      <c r="Q231" s="7" t="n"/>
+      <c r="R231" s="3">
+        <f>IF(OR(F231="",F231=0),"",(N(P231)+N(H231)+N(Q231)+N(I231))/F231*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -9095,6 +10557,12 @@
         <f>IF(OR(M232="",F232=0),"",M232/F232*10000)</f>
         <v/>
       </c>
+      <c r="P232" s="7" t="n"/>
+      <c r="Q232" s="7" t="n"/>
+      <c r="R232" s="3">
+        <f>IF(OR(F232="",F232=0),"",(N(P232)+N(H232)+N(Q232)+N(I232))/F232*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -9127,6 +10595,12 @@
         <f>IF(OR(M233="",F233=0),"",M233/F233*10000)</f>
         <v/>
       </c>
+      <c r="P233" s="7" t="n"/>
+      <c r="Q233" s="7" t="n"/>
+      <c r="R233" s="3">
+        <f>IF(OR(F233="",F233=0),"",(N(P233)+N(H233)+N(Q233)+N(I233))/F233*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -9159,6 +10633,12 @@
         <f>IF(OR(M234="",F234=0),"",M234/F234*10000)</f>
         <v/>
       </c>
+      <c r="P234" s="7" t="n"/>
+      <c r="Q234" s="7" t="n"/>
+      <c r="R234" s="3">
+        <f>IF(OR(F234="",F234=0),"",(N(P234)+N(H234)+N(Q234)+N(I234))/F234*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -9191,6 +10671,12 @@
         <f>IF(OR(M235="",F235=0),"",M235/F235*10000)</f>
         <v/>
       </c>
+      <c r="P235" s="7" t="n"/>
+      <c r="Q235" s="7" t="n"/>
+      <c r="R235" s="3">
+        <f>IF(OR(F235="",F235=0),"",(N(P235)+N(H235)+N(Q235)+N(I235))/F235*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -9223,6 +10709,12 @@
         <f>IF(OR(M236="",F236=0),"",M236/F236*10000)</f>
         <v/>
       </c>
+      <c r="P236" s="7" t="n"/>
+      <c r="Q236" s="7" t="n"/>
+      <c r="R236" s="3">
+        <f>IF(OR(F236="",F236=0),"",(N(P236)+N(H236)+N(Q236)+N(I236))/F236*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -9255,6 +10747,12 @@
         <f>IF(OR(M237="",F237=0),"",M237/F237*10000)</f>
         <v/>
       </c>
+      <c r="P237" s="7" t="n"/>
+      <c r="Q237" s="7" t="n"/>
+      <c r="R237" s="3">
+        <f>IF(OR(F237="",F237=0),"",(N(P237)+N(H237)+N(Q237)+N(I237))/F237*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -9287,6 +10785,12 @@
         <f>IF(OR(M238="",F238=0),"",M238/F238*10000)</f>
         <v/>
       </c>
+      <c r="P238" s="7" t="n"/>
+      <c r="Q238" s="7" t="n"/>
+      <c r="R238" s="3">
+        <f>IF(OR(F238="",F238=0),"",(N(P238)+N(H238)+N(Q238)+N(I238))/F238*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -9319,6 +10823,12 @@
         <f>IF(OR(M239="",F239=0),"",M239/F239*10000)</f>
         <v/>
       </c>
+      <c r="P239" s="7" t="n"/>
+      <c r="Q239" s="7" t="n"/>
+      <c r="R239" s="3">
+        <f>IF(OR(F239="",F239=0),"",(N(P239)+N(H239)+N(Q239)+N(I239))/F239*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -9351,6 +10861,12 @@
         <f>IF(OR(M240="",F240=0),"",M240/F240*10000)</f>
         <v/>
       </c>
+      <c r="P240" s="7" t="n"/>
+      <c r="Q240" s="7" t="n"/>
+      <c r="R240" s="3">
+        <f>IF(OR(F240="",F240=0),"",(N(P240)+N(H240)+N(Q240)+N(I240))/F240*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -9383,6 +10899,12 @@
         <f>IF(OR(M241="",F241=0),"",M241/F241*10000)</f>
         <v/>
       </c>
+      <c r="P241" s="7" t="n"/>
+      <c r="Q241" s="7" t="n"/>
+      <c r="R241" s="3">
+        <f>IF(OR(F241="",F241=0),"",(N(P241)+N(H241)+N(Q241)+N(I241))/F241*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -9415,6 +10937,12 @@
         <f>IF(OR(M242="",F242=0),"",M242/F242*10000)</f>
         <v/>
       </c>
+      <c r="P242" s="7" t="n"/>
+      <c r="Q242" s="7" t="n"/>
+      <c r="R242" s="3">
+        <f>IF(OR(F242="",F242=0),"",(N(P242)+N(H242)+N(Q242)+N(I242))/F242*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -9447,6 +10975,12 @@
         <f>IF(OR(M243="",F243=0),"",M243/F243*10000)</f>
         <v/>
       </c>
+      <c r="P243" s="7" t="n"/>
+      <c r="Q243" s="7" t="n"/>
+      <c r="R243" s="3">
+        <f>IF(OR(F243="",F243=0),"",(N(P243)+N(H243)+N(Q243)+N(I243))/F243*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -9479,6 +11013,12 @@
         <f>IF(OR(M244="",F244=0),"",M244/F244*10000)</f>
         <v/>
       </c>
+      <c r="P244" s="7" t="n"/>
+      <c r="Q244" s="7" t="n"/>
+      <c r="R244" s="3">
+        <f>IF(OR(F244="",F244=0),"",(N(P244)+N(H244)+N(Q244)+N(I244))/F244*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -9511,6 +11051,12 @@
         <f>IF(OR(M245="",F245=0),"",M245/F245*10000)</f>
         <v/>
       </c>
+      <c r="P245" s="7" t="n"/>
+      <c r="Q245" s="7" t="n"/>
+      <c r="R245" s="3">
+        <f>IF(OR(F245="",F245=0),"",(N(P245)+N(H245)+N(Q245)+N(I245))/F245*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -9543,6 +11089,12 @@
         <f>IF(OR(M246="",F246=0),"",M246/F246*10000)</f>
         <v/>
       </c>
+      <c r="P246" s="7" t="n"/>
+      <c r="Q246" s="7" t="n"/>
+      <c r="R246" s="3">
+        <f>IF(OR(F246="",F246=0),"",(N(P246)+N(H246)+N(Q246)+N(I246))/F246*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -9575,6 +11127,12 @@
         <f>IF(OR(M247="",F247=0),"",M247/F247*10000)</f>
         <v/>
       </c>
+      <c r="P247" s="7" t="n"/>
+      <c r="Q247" s="7" t="n"/>
+      <c r="R247" s="3">
+        <f>IF(OR(F247="",F247=0),"",(N(P247)+N(H247)+N(Q247)+N(I247))/F247*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -9607,6 +11165,12 @@
         <f>IF(OR(M248="",F248=0),"",M248/F248*10000)</f>
         <v/>
       </c>
+      <c r="P248" s="7" t="n"/>
+      <c r="Q248" s="7" t="n"/>
+      <c r="R248" s="3">
+        <f>IF(OR(F248="",F248=0),"",(N(P248)+N(H248)+N(Q248)+N(I248))/F248*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -9639,6 +11203,12 @@
         <f>IF(OR(M249="",F249=0),"",M249/F249*10000)</f>
         <v/>
       </c>
+      <c r="P249" s="7" t="n"/>
+      <c r="Q249" s="7" t="n"/>
+      <c r="R249" s="3">
+        <f>IF(OR(F249="",F249=0),"",(N(P249)+N(H249)+N(Q249)+N(I249))/F249*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -9671,6 +11241,12 @@
         <f>IF(OR(M250="",F250=0),"",M250/F250*10000)</f>
         <v/>
       </c>
+      <c r="P250" s="7" t="n"/>
+      <c r="Q250" s="7" t="n"/>
+      <c r="R250" s="3">
+        <f>IF(OR(F250="",F250=0),"",(N(P250)+N(H250)+N(Q250)+N(I250))/F250*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -9703,6 +11279,12 @@
         <f>IF(OR(M251="",F251=0),"",M251/F251*10000)</f>
         <v/>
       </c>
+      <c r="P251" s="7" t="n"/>
+      <c r="Q251" s="7" t="n"/>
+      <c r="R251" s="3">
+        <f>IF(OR(F251="",F251=0),"",(N(P251)+N(H251)+N(Q251)+N(I251))/F251*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -9735,6 +11317,12 @@
         <f>IF(OR(M252="",F252=0),"",M252/F252*10000)</f>
         <v/>
       </c>
+      <c r="P252" s="7" t="n"/>
+      <c r="Q252" s="7" t="n"/>
+      <c r="R252" s="3">
+        <f>IF(OR(F252="",F252=0),"",(N(P252)+N(H252)+N(Q252)+N(I252))/F252*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -9767,6 +11355,12 @@
         <f>IF(OR(M253="",F253=0),"",M253/F253*10000)</f>
         <v/>
       </c>
+      <c r="P253" s="7" t="n"/>
+      <c r="Q253" s="7" t="n"/>
+      <c r="R253" s="3">
+        <f>IF(OR(F253="",F253=0),"",(N(P253)+N(H253)+N(Q253)+N(I253))/F253*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -9799,6 +11393,12 @@
         <f>IF(OR(M254="",F254=0),"",M254/F254*10000)</f>
         <v/>
       </c>
+      <c r="P254" s="7" t="n"/>
+      <c r="Q254" s="7" t="n"/>
+      <c r="R254" s="3">
+        <f>IF(OR(F254="",F254=0),"",(N(P254)+N(H254)+N(Q254)+N(I254))/F254*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -9831,6 +11431,12 @@
         <f>IF(OR(M255="",F255=0),"",M255/F255*10000)</f>
         <v/>
       </c>
+      <c r="P255" s="7" t="n"/>
+      <c r="Q255" s="7" t="n"/>
+      <c r="R255" s="3">
+        <f>IF(OR(F255="",F255=0),"",(N(P255)+N(H255)+N(Q255)+N(I255))/F255*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -9863,6 +11469,12 @@
         <f>IF(OR(M256="",F256=0),"",M256/F256*10000)</f>
         <v/>
       </c>
+      <c r="P256" s="7" t="n"/>
+      <c r="Q256" s="7" t="n"/>
+      <c r="R256" s="3">
+        <f>IF(OR(F256="",F256=0),"",(N(P256)+N(H256)+N(Q256)+N(I256))/F256*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -9895,6 +11507,12 @@
         <f>IF(OR(M257="",F257=0),"",M257/F257*10000)</f>
         <v/>
       </c>
+      <c r="P257" s="7" t="n"/>
+      <c r="Q257" s="7" t="n"/>
+      <c r="R257" s="3">
+        <f>IF(OR(F257="",F257=0),"",(N(P257)+N(H257)+N(Q257)+N(I257))/F257*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -9927,6 +11545,12 @@
         <f>IF(OR(M258="",F258=0),"",M258/F258*10000)</f>
         <v/>
       </c>
+      <c r="P258" s="7" t="n"/>
+      <c r="Q258" s="7" t="n"/>
+      <c r="R258" s="3">
+        <f>IF(OR(F258="",F258=0),"",(N(P258)+N(H258)+N(Q258)+N(I258))/F258*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -9959,6 +11583,12 @@
         <f>IF(OR(M259="",F259=0),"",M259/F259*10000)</f>
         <v/>
       </c>
+      <c r="P259" s="7" t="n"/>
+      <c r="Q259" s="7" t="n"/>
+      <c r="R259" s="3">
+        <f>IF(OR(F259="",F259=0),"",(N(P259)+N(H259)+N(Q259)+N(I259))/F259*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -9991,6 +11621,12 @@
         <f>IF(OR(M260="",F260=0),"",M260/F260*10000)</f>
         <v/>
       </c>
+      <c r="P260" s="7" t="n"/>
+      <c r="Q260" s="7" t="n"/>
+      <c r="R260" s="3">
+        <f>IF(OR(F260="",F260=0),"",(N(P260)+N(H260)+N(Q260)+N(I260))/F260*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -10023,6 +11659,12 @@
         <f>IF(OR(M261="",F261=0),"",M261/F261*10000)</f>
         <v/>
       </c>
+      <c r="P261" s="7" t="n"/>
+      <c r="Q261" s="7" t="n"/>
+      <c r="R261" s="3">
+        <f>IF(OR(F261="",F261=0),"",(N(P261)+N(H261)+N(Q261)+N(I261))/F261*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -10055,6 +11697,12 @@
         <f>IF(OR(M262="",F262=0),"",M262/F262*10000)</f>
         <v/>
       </c>
+      <c r="P262" s="7" t="n"/>
+      <c r="Q262" s="7" t="n"/>
+      <c r="R262" s="3">
+        <f>IF(OR(F262="",F262=0),"",(N(P262)+N(H262)+N(Q262)+N(I262))/F262*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -10087,6 +11735,12 @@
         <f>IF(OR(M263="",F263=0),"",M263/F263*10000)</f>
         <v/>
       </c>
+      <c r="P263" s="7" t="n"/>
+      <c r="Q263" s="7" t="n"/>
+      <c r="R263" s="3">
+        <f>IF(OR(F263="",F263=0),"",(N(P263)+N(H263)+N(Q263)+N(I263))/F263*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -10119,6 +11773,12 @@
         <f>IF(OR(M264="",F264=0),"",M264/F264*10000)</f>
         <v/>
       </c>
+      <c r="P264" s="7" t="n"/>
+      <c r="Q264" s="7" t="n"/>
+      <c r="R264" s="3">
+        <f>IF(OR(F264="",F264=0),"",(N(P264)+N(H264)+N(Q264)+N(I264))/F264*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -10151,6 +11811,12 @@
         <f>IF(OR(M265="",F265=0),"",M265/F265*10000)</f>
         <v/>
       </c>
+      <c r="P265" s="7" t="n"/>
+      <c r="Q265" s="7" t="n"/>
+      <c r="R265" s="3">
+        <f>IF(OR(F265="",F265=0),"",(N(P265)+N(H265)+N(Q265)+N(I265))/F265*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -10183,6 +11849,12 @@
         <f>IF(OR(M266="",F266=0),"",M266/F266*10000)</f>
         <v/>
       </c>
+      <c r="P266" s="7" t="n"/>
+      <c r="Q266" s="7" t="n"/>
+      <c r="R266" s="3">
+        <f>IF(OR(F266="",F266=0),"",(N(P266)+N(H266)+N(Q266)+N(I266))/F266*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -10215,6 +11887,12 @@
         <f>IF(OR(M267="",F267=0),"",M267/F267*10000)</f>
         <v/>
       </c>
+      <c r="P267" s="7" t="n"/>
+      <c r="Q267" s="7" t="n"/>
+      <c r="R267" s="3">
+        <f>IF(OR(F267="",F267=0),"",(N(P267)+N(H267)+N(Q267)+N(I267))/F267*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -10247,6 +11925,12 @@
         <f>IF(OR(M268="",F268=0),"",M268/F268*10000)</f>
         <v/>
       </c>
+      <c r="P268" s="7" t="n"/>
+      <c r="Q268" s="7" t="n"/>
+      <c r="R268" s="3">
+        <f>IF(OR(F268="",F268=0),"",(N(P268)+N(H268)+N(Q268)+N(I268))/F268*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -10279,6 +11963,12 @@
         <f>IF(OR(M269="",F269=0),"",M269/F269*10000)</f>
         <v/>
       </c>
+      <c r="P269" s="7" t="n"/>
+      <c r="Q269" s="7" t="n"/>
+      <c r="R269" s="3">
+        <f>IF(OR(F269="",F269=0),"",(N(P269)+N(H269)+N(Q269)+N(I269))/F269*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -10311,6 +12001,12 @@
         <f>IF(OR(M270="",F270=0),"",M270/F270*10000)</f>
         <v/>
       </c>
+      <c r="P270" s="7" t="n"/>
+      <c r="Q270" s="7" t="n"/>
+      <c r="R270" s="3">
+        <f>IF(OR(F270="",F270=0),"",(N(P270)+N(H270)+N(Q270)+N(I270))/F270*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -10343,6 +12039,12 @@
         <f>IF(OR(M271="",F271=0),"",M271/F271*10000)</f>
         <v/>
       </c>
+      <c r="P271" s="7" t="n"/>
+      <c r="Q271" s="7" t="n"/>
+      <c r="R271" s="3">
+        <f>IF(OR(F271="",F271=0),"",(N(P271)+N(H271)+N(Q271)+N(I271))/F271*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -10375,6 +12077,12 @@
         <f>IF(OR(M272="",F272=0),"",M272/F272*10000)</f>
         <v/>
       </c>
+      <c r="P272" s="7" t="n"/>
+      <c r="Q272" s="7" t="n"/>
+      <c r="R272" s="3">
+        <f>IF(OR(F272="",F272=0),"",(N(P272)+N(H272)+N(Q272)+N(I272))/F272*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -10407,6 +12115,12 @@
         <f>IF(OR(M273="",F273=0),"",M273/F273*10000)</f>
         <v/>
       </c>
+      <c r="P273" s="7" t="n"/>
+      <c r="Q273" s="7" t="n"/>
+      <c r="R273" s="3">
+        <f>IF(OR(F273="",F273=0),"",(N(P273)+N(H273)+N(Q273)+N(I273))/F273*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -10439,6 +12153,12 @@
         <f>IF(OR(M274="",F274=0),"",M274/F274*10000)</f>
         <v/>
       </c>
+      <c r="P274" s="7" t="n"/>
+      <c r="Q274" s="7" t="n"/>
+      <c r="R274" s="3">
+        <f>IF(OR(F274="",F274=0),"",(N(P274)+N(H274)+N(Q274)+N(I274))/F274*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -10471,6 +12191,12 @@
         <f>IF(OR(M275="",F275=0),"",M275/F275*10000)</f>
         <v/>
       </c>
+      <c r="P275" s="7" t="n"/>
+      <c r="Q275" s="7" t="n"/>
+      <c r="R275" s="3">
+        <f>IF(OR(F275="",F275=0),"",(N(P275)+N(H275)+N(Q275)+N(I275))/F275*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -10503,6 +12229,12 @@
         <f>IF(OR(M276="",F276=0),"",M276/F276*10000)</f>
         <v/>
       </c>
+      <c r="P276" s="7" t="n"/>
+      <c r="Q276" s="7" t="n"/>
+      <c r="R276" s="3">
+        <f>IF(OR(F276="",F276=0),"",(N(P276)+N(H276)+N(Q276)+N(I276))/F276*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -10535,6 +12267,12 @@
         <f>IF(OR(M277="",F277=0),"",M277/F277*10000)</f>
         <v/>
       </c>
+      <c r="P277" s="7" t="n"/>
+      <c r="Q277" s="7" t="n"/>
+      <c r="R277" s="3">
+        <f>IF(OR(F277="",F277=0),"",(N(P277)+N(H277)+N(Q277)+N(I277))/F277*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -10567,6 +12305,12 @@
         <f>IF(OR(M278="",F278=0),"",M278/F278*10000)</f>
         <v/>
       </c>
+      <c r="P278" s="7" t="n"/>
+      <c r="Q278" s="7" t="n"/>
+      <c r="R278" s="3">
+        <f>IF(OR(F278="",F278=0),"",(N(P278)+N(H278)+N(Q278)+N(I278))/F278*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -10599,6 +12343,12 @@
         <f>IF(OR(M279="",F279=0),"",M279/F279*10000)</f>
         <v/>
       </c>
+      <c r="P279" s="7" t="n"/>
+      <c r="Q279" s="7" t="n"/>
+      <c r="R279" s="3">
+        <f>IF(OR(F279="",F279=0),"",(N(P279)+N(H279)+N(Q279)+N(I279))/F279*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -10631,6 +12381,12 @@
         <f>IF(OR(M280="",F280=0),"",M280/F280*10000)</f>
         <v/>
       </c>
+      <c r="P280" s="7" t="n"/>
+      <c r="Q280" s="7" t="n"/>
+      <c r="R280" s="3">
+        <f>IF(OR(F280="",F280=0),"",(N(P280)+N(H280)+N(Q280)+N(I280))/F280*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -10663,6 +12419,12 @@
         <f>IF(OR(M281="",F281=0),"",M281/F281*10000)</f>
         <v/>
       </c>
+      <c r="P281" s="7" t="n"/>
+      <c r="Q281" s="7" t="n"/>
+      <c r="R281" s="3">
+        <f>IF(OR(F281="",F281=0),"",(N(P281)+N(H281)+N(Q281)+N(I281))/F281*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -10695,6 +12457,12 @@
         <f>IF(OR(M282="",F282=0),"",M282/F282*10000)</f>
         <v/>
       </c>
+      <c r="P282" s="7" t="n"/>
+      <c r="Q282" s="7" t="n"/>
+      <c r="R282" s="3">
+        <f>IF(OR(F282="",F282=0),"",(N(P282)+N(H282)+N(Q282)+N(I282))/F282*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -10727,6 +12495,12 @@
         <f>IF(OR(M283="",F283=0),"",M283/F283*10000)</f>
         <v/>
       </c>
+      <c r="P283" s="7" t="n"/>
+      <c r="Q283" s="7" t="n"/>
+      <c r="R283" s="3">
+        <f>IF(OR(F283="",F283=0),"",(N(P283)+N(H283)+N(Q283)+N(I283))/F283*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -10759,6 +12533,12 @@
         <f>IF(OR(M284="",F284=0),"",M284/F284*10000)</f>
         <v/>
       </c>
+      <c r="P284" s="7" t="n"/>
+      <c r="Q284" s="7" t="n"/>
+      <c r="R284" s="3">
+        <f>IF(OR(F284="",F284=0),"",(N(P284)+N(H284)+N(Q284)+N(I284))/F284*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -10791,6 +12571,12 @@
         <f>IF(OR(M285="",F285=0),"",M285/F285*10000)</f>
         <v/>
       </c>
+      <c r="P285" s="7" t="n"/>
+      <c r="Q285" s="7" t="n"/>
+      <c r="R285" s="3">
+        <f>IF(OR(F285="",F285=0),"",(N(P285)+N(H285)+N(Q285)+N(I285))/F285*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -10823,6 +12609,12 @@
         <f>IF(OR(M286="",F286=0),"",M286/F286*10000)</f>
         <v/>
       </c>
+      <c r="P286" s="7" t="n"/>
+      <c r="Q286" s="7" t="n"/>
+      <c r="R286" s="3">
+        <f>IF(OR(F286="",F286=0),"",(N(P286)+N(H286)+N(Q286)+N(I286))/F286*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -10855,6 +12647,12 @@
         <f>IF(OR(M287="",F287=0),"",M287/F287*10000)</f>
         <v/>
       </c>
+      <c r="P287" s="7" t="n"/>
+      <c r="Q287" s="7" t="n"/>
+      <c r="R287" s="3">
+        <f>IF(OR(F287="",F287=0),"",(N(P287)+N(H287)+N(Q287)+N(I287))/F287*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -10887,6 +12685,12 @@
         <f>IF(OR(M288="",F288=0),"",M288/F288*10000)</f>
         <v/>
       </c>
+      <c r="P288" s="7" t="n"/>
+      <c r="Q288" s="7" t="n"/>
+      <c r="R288" s="3">
+        <f>IF(OR(F288="",F288=0),"",(N(P288)+N(H288)+N(Q288)+N(I288))/F288*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -10919,6 +12723,12 @@
         <f>IF(OR(M289="",F289=0),"",M289/F289*10000)</f>
         <v/>
       </c>
+      <c r="P289" s="7" t="n"/>
+      <c r="Q289" s="7" t="n"/>
+      <c r="R289" s="3">
+        <f>IF(OR(F289="",F289=0),"",(N(P289)+N(H289)+N(Q289)+N(I289))/F289*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -10951,6 +12761,12 @@
         <f>IF(OR(M290="",F290=0),"",M290/F290*10000)</f>
         <v/>
       </c>
+      <c r="P290" s="7" t="n"/>
+      <c r="Q290" s="7" t="n"/>
+      <c r="R290" s="3">
+        <f>IF(OR(F290="",F290=0),"",(N(P290)+N(H290)+N(Q290)+N(I290))/F290*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -10983,6 +12799,12 @@
         <f>IF(OR(M291="",F291=0),"",M291/F291*10000)</f>
         <v/>
       </c>
+      <c r="P291" s="7" t="n"/>
+      <c r="Q291" s="7" t="n"/>
+      <c r="R291" s="3">
+        <f>IF(OR(F291="",F291=0),"",(N(P291)+N(H291)+N(Q291)+N(I291))/F291*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -11015,6 +12837,12 @@
         <f>IF(OR(M292="",F292=0),"",M292/F292*10000)</f>
         <v/>
       </c>
+      <c r="P292" s="7" t="n"/>
+      <c r="Q292" s="7" t="n"/>
+      <c r="R292" s="3">
+        <f>IF(OR(F292="",F292=0),"",(N(P292)+N(H292)+N(Q292)+N(I292))/F292*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -11047,6 +12875,12 @@
         <f>IF(OR(M293="",F293=0),"",M293/F293*10000)</f>
         <v/>
       </c>
+      <c r="P293" s="7" t="n"/>
+      <c r="Q293" s="7" t="n"/>
+      <c r="R293" s="3">
+        <f>IF(OR(F293="",F293=0),"",(N(P293)+N(H293)+N(Q293)+N(I293))/F293*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -11079,6 +12913,12 @@
         <f>IF(OR(M294="",F294=0),"",M294/F294*10000)</f>
         <v/>
       </c>
+      <c r="P294" s="7" t="n"/>
+      <c r="Q294" s="7" t="n"/>
+      <c r="R294" s="3">
+        <f>IF(OR(F294="",F294=0),"",(N(P294)+N(H294)+N(Q294)+N(I294))/F294*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -11111,6 +12951,12 @@
         <f>IF(OR(M295="",F295=0),"",M295/F295*10000)</f>
         <v/>
       </c>
+      <c r="P295" s="7" t="n"/>
+      <c r="Q295" s="7" t="n"/>
+      <c r="R295" s="3">
+        <f>IF(OR(F295="",F295=0),"",(N(P295)+N(H295)+N(Q295)+N(I295))/F295*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -11143,6 +12989,12 @@
         <f>IF(OR(M296="",F296=0),"",M296/F296*10000)</f>
         <v/>
       </c>
+      <c r="P296" s="7" t="n"/>
+      <c r="Q296" s="7" t="n"/>
+      <c r="R296" s="3">
+        <f>IF(OR(F296="",F296=0),"",(N(P296)+N(H296)+N(Q296)+N(I296))/F296*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -11175,6 +13027,12 @@
         <f>IF(OR(M297="",F297=0),"",M297/F297*10000)</f>
         <v/>
       </c>
+      <c r="P297" s="7" t="n"/>
+      <c r="Q297" s="7" t="n"/>
+      <c r="R297" s="3">
+        <f>IF(OR(F297="",F297=0),"",(N(P297)+N(H297)+N(Q297)+N(I297))/F297*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -11207,6 +13065,12 @@
         <f>IF(OR(M298="",F298=0),"",M298/F298*10000)</f>
         <v/>
       </c>
+      <c r="P298" s="7" t="n"/>
+      <c r="Q298" s="7" t="n"/>
+      <c r="R298" s="3">
+        <f>IF(OR(F298="",F298=0),"",(N(P298)+N(H298)+N(Q298)+N(I298))/F298*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -11239,6 +13103,12 @@
         <f>IF(OR(M299="",F299=0),"",M299/F299*10000)</f>
         <v/>
       </c>
+      <c r="P299" s="7" t="n"/>
+      <c r="Q299" s="7" t="n"/>
+      <c r="R299" s="3">
+        <f>IF(OR(F299="",F299=0),"",(N(P299)+N(H299)+N(Q299)+N(I299))/F299*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -11271,6 +13141,12 @@
         <f>IF(OR(M300="",F300=0),"",M300/F300*10000)</f>
         <v/>
       </c>
+      <c r="P300" s="7" t="n"/>
+      <c r="Q300" s="7" t="n"/>
+      <c r="R300" s="3">
+        <f>IF(OR(F300="",F300=0),"",(N(P300)+N(H300)+N(Q300)+N(I300))/F300*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -11303,6 +13179,12 @@
         <f>IF(OR(M301="",F301=0),"",M301/F301*10000)</f>
         <v/>
       </c>
+      <c r="P301" s="7" t="n"/>
+      <c r="Q301" s="7" t="n"/>
+      <c r="R301" s="3">
+        <f>IF(OR(F301="",F301=0),"",(N(P301)+N(H301)+N(Q301)+N(I301))/F301*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -11335,6 +13217,12 @@
         <f>IF(OR(M302="",F302=0),"",M302/F302*10000)</f>
         <v/>
       </c>
+      <c r="P302" s="7" t="n"/>
+      <c r="Q302" s="7" t="n"/>
+      <c r="R302" s="3">
+        <f>IF(OR(F302="",F302=0),"",(N(P302)+N(H302)+N(Q302)+N(I302))/F302*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -11367,6 +13255,12 @@
         <f>IF(OR(M303="",F303=0),"",M303/F303*10000)</f>
         <v/>
       </c>
+      <c r="P303" s="7" t="n"/>
+      <c r="Q303" s="7" t="n"/>
+      <c r="R303" s="3">
+        <f>IF(OR(F303="",F303=0),"",(N(P303)+N(H303)+N(Q303)+N(I303))/F303*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -11399,6 +13293,12 @@
         <f>IF(OR(M304="",F304=0),"",M304/F304*10000)</f>
         <v/>
       </c>
+      <c r="P304" s="7" t="n"/>
+      <c r="Q304" s="7" t="n"/>
+      <c r="R304" s="3">
+        <f>IF(OR(F304="",F304=0),"",(N(P304)+N(H304)+N(Q304)+N(I304))/F304*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -11431,6 +13331,12 @@
         <f>IF(OR(M305="",F305=0),"",M305/F305*10000)</f>
         <v/>
       </c>
+      <c r="P305" s="7" t="n"/>
+      <c r="Q305" s="7" t="n"/>
+      <c r="R305" s="3">
+        <f>IF(OR(F305="",F305=0),"",(N(P305)+N(H305)+N(Q305)+N(I305))/F305*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -11463,6 +13369,12 @@
         <f>IF(OR(M306="",F306=0),"",M306/F306*10000)</f>
         <v/>
       </c>
+      <c r="P306" s="7" t="n"/>
+      <c r="Q306" s="7" t="n"/>
+      <c r="R306" s="3">
+        <f>IF(OR(F306="",F306=0),"",(N(P306)+N(H306)+N(Q306)+N(I306))/F306*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -11495,6 +13407,12 @@
         <f>IF(OR(M307="",F307=0),"",M307/F307*10000)</f>
         <v/>
       </c>
+      <c r="P307" s="7" t="n"/>
+      <c r="Q307" s="7" t="n"/>
+      <c r="R307" s="3">
+        <f>IF(OR(F307="",F307=0),"",(N(P307)+N(H307)+N(Q307)+N(I307))/F307*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -11527,6 +13445,12 @@
         <f>IF(OR(M308="",F308=0),"",M308/F308*10000)</f>
         <v/>
       </c>
+      <c r="P308" s="7" t="n"/>
+      <c r="Q308" s="7" t="n"/>
+      <c r="R308" s="3">
+        <f>IF(OR(F308="",F308=0),"",(N(P308)+N(H308)+N(Q308)+N(I308))/F308*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -11559,6 +13483,12 @@
         <f>IF(OR(M309="",F309=0),"",M309/F309*10000)</f>
         <v/>
       </c>
+      <c r="P309" s="7" t="n"/>
+      <c r="Q309" s="7" t="n"/>
+      <c r="R309" s="3">
+        <f>IF(OR(F309="",F309=0),"",(N(P309)+N(H309)+N(Q309)+N(I309))/F309*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -11591,6 +13521,12 @@
         <f>IF(OR(M310="",F310=0),"",M310/F310*10000)</f>
         <v/>
       </c>
+      <c r="P310" s="7" t="n"/>
+      <c r="Q310" s="7" t="n"/>
+      <c r="R310" s="3">
+        <f>IF(OR(F310="",F310=0),"",(N(P310)+N(H310)+N(Q310)+N(I310))/F310*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -11623,6 +13559,12 @@
         <f>IF(OR(M311="",F311=0),"",M311/F311*10000)</f>
         <v/>
       </c>
+      <c r="P311" s="7" t="n"/>
+      <c r="Q311" s="7" t="n"/>
+      <c r="R311" s="3">
+        <f>IF(OR(F311="",F311=0),"",(N(P311)+N(H311)+N(Q311)+N(I311))/F311*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -11655,6 +13597,12 @@
         <f>IF(OR(M312="",F312=0),"",M312/F312*10000)</f>
         <v/>
       </c>
+      <c r="P312" s="7" t="n"/>
+      <c r="Q312" s="7" t="n"/>
+      <c r="R312" s="3">
+        <f>IF(OR(F312="",F312=0),"",(N(P312)+N(H312)+N(Q312)+N(I312))/F312*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -11687,6 +13635,12 @@
         <f>IF(OR(M313="",F313=0),"",M313/F313*10000)</f>
         <v/>
       </c>
+      <c r="P313" s="7" t="n"/>
+      <c r="Q313" s="7" t="n"/>
+      <c r="R313" s="3">
+        <f>IF(OR(F313="",F313=0),"",(N(P313)+N(H313)+N(Q313)+N(I313))/F313*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -11719,6 +13673,12 @@
         <f>IF(OR(M314="",F314=0),"",M314/F314*10000)</f>
         <v/>
       </c>
+      <c r="P314" s="7" t="n"/>
+      <c r="Q314" s="7" t="n"/>
+      <c r="R314" s="3">
+        <f>IF(OR(F314="",F314=0),"",(N(P314)+N(H314)+N(Q314)+N(I314))/F314*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -11751,6 +13711,12 @@
         <f>IF(OR(M315="",F315=0),"",M315/F315*10000)</f>
         <v/>
       </c>
+      <c r="P315" s="7" t="n"/>
+      <c r="Q315" s="7" t="n"/>
+      <c r="R315" s="3">
+        <f>IF(OR(F315="",F315=0),"",(N(P315)+N(H315)+N(Q315)+N(I315))/F315*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -11783,6 +13749,12 @@
         <f>IF(OR(M316="",F316=0),"",M316/F316*10000)</f>
         <v/>
       </c>
+      <c r="P316" s="7" t="n"/>
+      <c r="Q316" s="7" t="n"/>
+      <c r="R316" s="3">
+        <f>IF(OR(F316="",F316=0),"",(N(P316)+N(H316)+N(Q316)+N(I316))/F316*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -11815,6 +13787,12 @@
         <f>IF(OR(M317="",F317=0),"",M317/F317*10000)</f>
         <v/>
       </c>
+      <c r="P317" s="7" t="n"/>
+      <c r="Q317" s="7" t="n"/>
+      <c r="R317" s="3">
+        <f>IF(OR(F317="",F317=0),"",(N(P317)+N(H317)+N(Q317)+N(I317))/F317*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -11847,6 +13825,12 @@
         <f>IF(OR(M318="",F318=0),"",M318/F318*10000)</f>
         <v/>
       </c>
+      <c r="P318" s="7" t="n"/>
+      <c r="Q318" s="7" t="n"/>
+      <c r="R318" s="3">
+        <f>IF(OR(F318="",F318=0),"",(N(P318)+N(H318)+N(Q318)+N(I318))/F318*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -11879,6 +13863,12 @@
         <f>IF(OR(M319="",F319=0),"",M319/F319*10000)</f>
         <v/>
       </c>
+      <c r="P319" s="7" t="n"/>
+      <c r="Q319" s="7" t="n"/>
+      <c r="R319" s="3">
+        <f>IF(OR(F319="",F319=0),"",(N(P319)+N(H319)+N(Q319)+N(I319))/F319*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -11911,6 +13901,12 @@
         <f>IF(OR(M320="",F320=0),"",M320/F320*10000)</f>
         <v/>
       </c>
+      <c r="P320" s="7" t="n"/>
+      <c r="Q320" s="7" t="n"/>
+      <c r="R320" s="3">
+        <f>IF(OR(F320="",F320=0),"",(N(P320)+N(H320)+N(Q320)+N(I320))/F320*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -11943,6 +13939,12 @@
         <f>IF(OR(M321="",F321=0),"",M321/F321*10000)</f>
         <v/>
       </c>
+      <c r="P321" s="7" t="n"/>
+      <c r="Q321" s="7" t="n"/>
+      <c r="R321" s="3">
+        <f>IF(OR(F321="",F321=0),"",(N(P321)+N(H321)+N(Q321)+N(I321))/F321*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -11975,6 +13977,12 @@
         <f>IF(OR(M322="",F322=0),"",M322/F322*10000)</f>
         <v/>
       </c>
+      <c r="P322" s="7" t="n"/>
+      <c r="Q322" s="7" t="n"/>
+      <c r="R322" s="3">
+        <f>IF(OR(F322="",F322=0),"",(N(P322)+N(H322)+N(Q322)+N(I322))/F322*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -12007,6 +14015,12 @@
         <f>IF(OR(M323="",F323=0),"",M323/F323*10000)</f>
         <v/>
       </c>
+      <c r="P323" s="7" t="n"/>
+      <c r="Q323" s="7" t="n"/>
+      <c r="R323" s="3">
+        <f>IF(OR(F323="",F323=0),"",(N(P323)+N(H323)+N(Q323)+N(I323))/F323*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -12039,6 +14053,12 @@
         <f>IF(OR(M324="",F324=0),"",M324/F324*10000)</f>
         <v/>
       </c>
+      <c r="P324" s="7" t="n"/>
+      <c r="Q324" s="7" t="n"/>
+      <c r="R324" s="3">
+        <f>IF(OR(F324="",F324=0),"",(N(P324)+N(H324)+N(Q324)+N(I324))/F324*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -12071,6 +14091,12 @@
         <f>IF(OR(M325="",F325=0),"",M325/F325*10000)</f>
         <v/>
       </c>
+      <c r="P325" s="7" t="n"/>
+      <c r="Q325" s="7" t="n"/>
+      <c r="R325" s="3">
+        <f>IF(OR(F325="",F325=0),"",(N(P325)+N(H325)+N(Q325)+N(I325))/F325*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -12103,6 +14129,12 @@
         <f>IF(OR(M326="",F326=0),"",M326/F326*10000)</f>
         <v/>
       </c>
+      <c r="P326" s="7" t="n"/>
+      <c r="Q326" s="7" t="n"/>
+      <c r="R326" s="3">
+        <f>IF(OR(F326="",F326=0),"",(N(P326)+N(H326)+N(Q326)+N(I326))/F326*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -12135,6 +14167,12 @@
         <f>IF(OR(M327="",F327=0),"",M327/F327*10000)</f>
         <v/>
       </c>
+      <c r="P327" s="7" t="n"/>
+      <c r="Q327" s="7" t="n"/>
+      <c r="R327" s="3">
+        <f>IF(OR(F327="",F327=0),"",(N(P327)+N(H327)+N(Q327)+N(I327))/F327*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -12167,6 +14205,12 @@
         <f>IF(OR(M328="",F328=0),"",M328/F328*10000)</f>
         <v/>
       </c>
+      <c r="P328" s="7" t="n"/>
+      <c r="Q328" s="7" t="n"/>
+      <c r="R328" s="3">
+        <f>IF(OR(F328="",F328=0),"",(N(P328)+N(H328)+N(Q328)+N(I328))/F328*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -12199,6 +14243,12 @@
         <f>IF(OR(M329="",F329=0),"",M329/F329*10000)</f>
         <v/>
       </c>
+      <c r="P329" s="7" t="n"/>
+      <c r="Q329" s="7" t="n"/>
+      <c r="R329" s="3">
+        <f>IF(OR(F329="",F329=0),"",(N(P329)+N(H329)+N(Q329)+N(I329))/F329*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -12231,6 +14281,12 @@
         <f>IF(OR(M330="",F330=0),"",M330/F330*10000)</f>
         <v/>
       </c>
+      <c r="P330" s="7" t="n"/>
+      <c r="Q330" s="7" t="n"/>
+      <c r="R330" s="3">
+        <f>IF(OR(F330="",F330=0),"",(N(P330)+N(H330)+N(Q330)+N(I330))/F330*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -12263,6 +14319,12 @@
         <f>IF(OR(M331="",F331=0),"",M331/F331*10000)</f>
         <v/>
       </c>
+      <c r="P331" s="7" t="n"/>
+      <c r="Q331" s="7" t="n"/>
+      <c r="R331" s="3">
+        <f>IF(OR(F331="",F331=0),"",(N(P331)+N(H331)+N(Q331)+N(I331))/F331*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -12295,6 +14357,12 @@
         <f>IF(OR(M332="",F332=0),"",M332/F332*10000)</f>
         <v/>
       </c>
+      <c r="P332" s="7" t="n"/>
+      <c r="Q332" s="7" t="n"/>
+      <c r="R332" s="3">
+        <f>IF(OR(F332="",F332=0),"",(N(P332)+N(H332)+N(Q332)+N(I332))/F332*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -12327,6 +14395,12 @@
         <f>IF(OR(M333="",F333=0),"",M333/F333*10000)</f>
         <v/>
       </c>
+      <c r="P333" s="7" t="n"/>
+      <c r="Q333" s="7" t="n"/>
+      <c r="R333" s="3">
+        <f>IF(OR(F333="",F333=0),"",(N(P333)+N(H333)+N(Q333)+N(I333))/F333*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -12359,6 +14433,12 @@
         <f>IF(OR(M334="",F334=0),"",M334/F334*10000)</f>
         <v/>
       </c>
+      <c r="P334" s="7" t="n"/>
+      <c r="Q334" s="7" t="n"/>
+      <c r="R334" s="3">
+        <f>IF(OR(F334="",F334=0),"",(N(P334)+N(H334)+N(Q334)+N(I334))/F334*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -12391,6 +14471,12 @@
         <f>IF(OR(M335="",F335=0),"",M335/F335*10000)</f>
         <v/>
       </c>
+      <c r="P335" s="7" t="n"/>
+      <c r="Q335" s="7" t="n"/>
+      <c r="R335" s="3">
+        <f>IF(OR(F335="",F335=0),"",(N(P335)+N(H335)+N(Q335)+N(I335))/F335*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -12423,6 +14509,12 @@
         <f>IF(OR(M336="",F336=0),"",M336/F336*10000)</f>
         <v/>
       </c>
+      <c r="P336" s="7" t="n"/>
+      <c r="Q336" s="7" t="n"/>
+      <c r="R336" s="3">
+        <f>IF(OR(F336="",F336=0),"",(N(P336)+N(H336)+N(Q336)+N(I336))/F336*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -12455,6 +14547,12 @@
         <f>IF(OR(M337="",F337=0),"",M337/F337*10000)</f>
         <v/>
       </c>
+      <c r="P337" s="7" t="n"/>
+      <c r="Q337" s="7" t="n"/>
+      <c r="R337" s="3">
+        <f>IF(OR(F337="",F337=0),"",(N(P337)+N(H337)+N(Q337)+N(I337))/F337*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -12487,6 +14585,12 @@
         <f>IF(OR(M338="",F338=0),"",M338/F338*10000)</f>
         <v/>
       </c>
+      <c r="P338" s="7" t="n"/>
+      <c r="Q338" s="7" t="n"/>
+      <c r="R338" s="3">
+        <f>IF(OR(F338="",F338=0),"",(N(P338)+N(H338)+N(Q338)+N(I338))/F338*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -12519,6 +14623,12 @@
         <f>IF(OR(M339="",F339=0),"",M339/F339*10000)</f>
         <v/>
       </c>
+      <c r="P339" s="7" t="n"/>
+      <c r="Q339" s="7" t="n"/>
+      <c r="R339" s="3">
+        <f>IF(OR(F339="",F339=0),"",(N(P339)+N(H339)+N(Q339)+N(I339))/F339*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -12551,6 +14661,12 @@
         <f>IF(OR(M340="",F340=0),"",M340/F340*10000)</f>
         <v/>
       </c>
+      <c r="P340" s="7" t="n"/>
+      <c r="Q340" s="7" t="n"/>
+      <c r="R340" s="3">
+        <f>IF(OR(F340="",F340=0),"",(N(P340)+N(H340)+N(Q340)+N(I340))/F340*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -12583,6 +14699,12 @@
         <f>IF(OR(M341="",F341=0),"",M341/F341*10000)</f>
         <v/>
       </c>
+      <c r="P341" s="7" t="n"/>
+      <c r="Q341" s="7" t="n"/>
+      <c r="R341" s="3">
+        <f>IF(OR(F341="",F341=0),"",(N(P341)+N(H341)+N(Q341)+N(I341))/F341*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -12615,6 +14737,12 @@
         <f>IF(OR(M342="",F342=0),"",M342/F342*10000)</f>
         <v/>
       </c>
+      <c r="P342" s="7" t="n"/>
+      <c r="Q342" s="7" t="n"/>
+      <c r="R342" s="3">
+        <f>IF(OR(F342="",F342=0),"",(N(P342)+N(H342)+N(Q342)+N(I342))/F342*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -12647,6 +14775,12 @@
         <f>IF(OR(M343="",F343=0),"",M343/F343*10000)</f>
         <v/>
       </c>
+      <c r="P343" s="7" t="n"/>
+      <c r="Q343" s="7" t="n"/>
+      <c r="R343" s="3">
+        <f>IF(OR(F343="",F343=0),"",(N(P343)+N(H343)+N(Q343)+N(I343))/F343*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -12679,6 +14813,12 @@
         <f>IF(OR(M344="",F344=0),"",M344/F344*10000)</f>
         <v/>
       </c>
+      <c r="P344" s="7" t="n"/>
+      <c r="Q344" s="7" t="n"/>
+      <c r="R344" s="3">
+        <f>IF(OR(F344="",F344=0),"",(N(P344)+N(H344)+N(Q344)+N(I344))/F344*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="7" t="n"/>
@@ -12711,6 +14851,12 @@
         <f>IF(OR(M345="",F345=0),"",M345/F345*10000)</f>
         <v/>
       </c>
+      <c r="P345" s="7" t="n"/>
+      <c r="Q345" s="7" t="n"/>
+      <c r="R345" s="3">
+        <f>IF(OR(F345="",F345=0),"",(N(P345)+N(H345)+N(Q345)+N(I345))/F345*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="n"/>
@@ -12743,6 +14889,12 @@
         <f>IF(OR(M346="",F346=0),"",M346/F346*10000)</f>
         <v/>
       </c>
+      <c r="P346" s="7" t="n"/>
+      <c r="Q346" s="7" t="n"/>
+      <c r="R346" s="3">
+        <f>IF(OR(F346="",F346=0),"",(N(P346)+N(H346)+N(Q346)+N(I346))/F346*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="n"/>
@@ -12775,6 +14927,12 @@
         <f>IF(OR(M347="",F347=0),"",M347/F347*10000)</f>
         <v/>
       </c>
+      <c r="P347" s="7" t="n"/>
+      <c r="Q347" s="7" t="n"/>
+      <c r="R347" s="3">
+        <f>IF(OR(F347="",F347=0),"",(N(P347)+N(H347)+N(Q347)+N(I347))/F347*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -12807,6 +14965,12 @@
         <f>IF(OR(M348="",F348=0),"",M348/F348*10000)</f>
         <v/>
       </c>
+      <c r="P348" s="7" t="n"/>
+      <c r="Q348" s="7" t="n"/>
+      <c r="R348" s="3">
+        <f>IF(OR(F348="",F348=0),"",(N(P348)+N(H348)+N(Q348)+N(I348))/F348*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -12839,6 +15003,12 @@
         <f>IF(OR(M349="",F349=0),"",M349/F349*10000)</f>
         <v/>
       </c>
+      <c r="P349" s="7" t="n"/>
+      <c r="Q349" s="7" t="n"/>
+      <c r="R349" s="3">
+        <f>IF(OR(F349="",F349=0),"",(N(P349)+N(H349)+N(Q349)+N(I349))/F349*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -12871,6 +15041,12 @@
         <f>IF(OR(M350="",F350=0),"",M350/F350*10000)</f>
         <v/>
       </c>
+      <c r="P350" s="7" t="n"/>
+      <c r="Q350" s="7" t="n"/>
+      <c r="R350" s="3">
+        <f>IF(OR(F350="",F350=0),"",(N(P350)+N(H350)+N(Q350)+N(I350))/F350*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -12903,6 +15079,12 @@
         <f>IF(OR(M351="",F351=0),"",M351/F351*10000)</f>
         <v/>
       </c>
+      <c r="P351" s="7" t="n"/>
+      <c r="Q351" s="7" t="n"/>
+      <c r="R351" s="3">
+        <f>IF(OR(F351="",F351=0),"",(N(P351)+N(H351)+N(Q351)+N(I351))/F351*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -12935,6 +15117,12 @@
         <f>IF(OR(M352="",F352=0),"",M352/F352*10000)</f>
         <v/>
       </c>
+      <c r="P352" s="7" t="n"/>
+      <c r="Q352" s="7" t="n"/>
+      <c r="R352" s="3">
+        <f>IF(OR(F352="",F352=0),"",(N(P352)+N(H352)+N(Q352)+N(I352))/F352*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -12967,6 +15155,12 @@
         <f>IF(OR(M353="",F353=0),"",M353/F353*10000)</f>
         <v/>
       </c>
+      <c r="P353" s="7" t="n"/>
+      <c r="Q353" s="7" t="n"/>
+      <c r="R353" s="3">
+        <f>IF(OR(F353="",F353=0),"",(N(P353)+N(H353)+N(Q353)+N(I353))/F353*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -12999,6 +15193,12 @@
         <f>IF(OR(M354="",F354=0),"",M354/F354*10000)</f>
         <v/>
       </c>
+      <c r="P354" s="7" t="n"/>
+      <c r="Q354" s="7" t="n"/>
+      <c r="R354" s="3">
+        <f>IF(OR(F354="",F354=0),"",(N(P354)+N(H354)+N(Q354)+N(I354))/F354*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -13031,6 +15231,12 @@
         <f>IF(OR(M355="",F355=0),"",M355/F355*10000)</f>
         <v/>
       </c>
+      <c r="P355" s="7" t="n"/>
+      <c r="Q355" s="7" t="n"/>
+      <c r="R355" s="3">
+        <f>IF(OR(F355="",F355=0),"",(N(P355)+N(H355)+N(Q355)+N(I355))/F355*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -13063,6 +15269,12 @@
         <f>IF(OR(M356="",F356=0),"",M356/F356*10000)</f>
         <v/>
       </c>
+      <c r="P356" s="7" t="n"/>
+      <c r="Q356" s="7" t="n"/>
+      <c r="R356" s="3">
+        <f>IF(OR(F356="",F356=0),"",(N(P356)+N(H356)+N(Q356)+N(I356))/F356*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -13095,6 +15307,12 @@
         <f>IF(OR(M357="",F357=0),"",M357/F357*10000)</f>
         <v/>
       </c>
+      <c r="P357" s="7" t="n"/>
+      <c r="Q357" s="7" t="n"/>
+      <c r="R357" s="3">
+        <f>IF(OR(F357="",F357=0),"",(N(P357)+N(H357)+N(Q357)+N(I357))/F357*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -13127,6 +15345,12 @@
         <f>IF(OR(M358="",F358=0),"",M358/F358*10000)</f>
         <v/>
       </c>
+      <c r="P358" s="7" t="n"/>
+      <c r="Q358" s="7" t="n"/>
+      <c r="R358" s="3">
+        <f>IF(OR(F358="",F358=0),"",(N(P358)+N(H358)+N(Q358)+N(I358))/F358*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -13159,6 +15383,12 @@
         <f>IF(OR(M359="",F359=0),"",M359/F359*10000)</f>
         <v/>
       </c>
+      <c r="P359" s="7" t="n"/>
+      <c r="Q359" s="7" t="n"/>
+      <c r="R359" s="3">
+        <f>IF(OR(F359="",F359=0),"",(N(P359)+N(H359)+N(Q359)+N(I359))/F359*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -13191,6 +15421,12 @@
         <f>IF(OR(M360="",F360=0),"",M360/F360*10000)</f>
         <v/>
       </c>
+      <c r="P360" s="7" t="n"/>
+      <c r="Q360" s="7" t="n"/>
+      <c r="R360" s="3">
+        <f>IF(OR(F360="",F360=0),"",(N(P360)+N(H360)+N(Q360)+N(I360))/F360*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -13223,6 +15459,12 @@
         <f>IF(OR(M361="",F361=0),"",M361/F361*10000)</f>
         <v/>
       </c>
+      <c r="P361" s="7" t="n"/>
+      <c r="Q361" s="7" t="n"/>
+      <c r="R361" s="3">
+        <f>IF(OR(F361="",F361=0),"",(N(P361)+N(H361)+N(Q361)+N(I361))/F361*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -13255,6 +15497,12 @@
         <f>IF(OR(M362="",F362=0),"",M362/F362*10000)</f>
         <v/>
       </c>
+      <c r="P362" s="7" t="n"/>
+      <c r="Q362" s="7" t="n"/>
+      <c r="R362" s="3">
+        <f>IF(OR(F362="",F362=0),"",(N(P362)+N(H362)+N(Q362)+N(I362))/F362*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -13287,6 +15535,12 @@
         <f>IF(OR(M363="",F363=0),"",M363/F363*10000)</f>
         <v/>
       </c>
+      <c r="P363" s="7" t="n"/>
+      <c r="Q363" s="7" t="n"/>
+      <c r="R363" s="3">
+        <f>IF(OR(F363="",F363=0),"",(N(P363)+N(H363)+N(Q363)+N(I363))/F363*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -13319,6 +15573,12 @@
         <f>IF(OR(M364="",F364=0),"",M364/F364*10000)</f>
         <v/>
       </c>
+      <c r="P364" s="7" t="n"/>
+      <c r="Q364" s="7" t="n"/>
+      <c r="R364" s="3">
+        <f>IF(OR(F364="",F364=0),"",(N(P364)+N(H364)+N(Q364)+N(I364))/F364*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -13351,6 +15611,12 @@
         <f>IF(OR(M365="",F365=0),"",M365/F365*10000)</f>
         <v/>
       </c>
+      <c r="P365" s="7" t="n"/>
+      <c r="Q365" s="7" t="n"/>
+      <c r="R365" s="3">
+        <f>IF(OR(F365="",F365=0),"",(N(P365)+N(H365)+N(Q365)+N(I365))/F365*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -13383,6 +15649,12 @@
         <f>IF(OR(M366="",F366=0),"",M366/F366*10000)</f>
         <v/>
       </c>
+      <c r="P366" s="7" t="n"/>
+      <c r="Q366" s="7" t="n"/>
+      <c r="R366" s="3">
+        <f>IF(OR(F366="",F366=0),"",(N(P366)+N(H366)+N(Q366)+N(I366))/F366*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -13415,6 +15687,12 @@
         <f>IF(OR(M367="",F367=0),"",M367/F367*10000)</f>
         <v/>
       </c>
+      <c r="P367" s="7" t="n"/>
+      <c r="Q367" s="7" t="n"/>
+      <c r="R367" s="3">
+        <f>IF(OR(F367="",F367=0),"",(N(P367)+N(H367)+N(Q367)+N(I367))/F367*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -13447,6 +15725,12 @@
         <f>IF(OR(M368="",F368=0),"",M368/F368*10000)</f>
         <v/>
       </c>
+      <c r="P368" s="7" t="n"/>
+      <c r="Q368" s="7" t="n"/>
+      <c r="R368" s="3">
+        <f>IF(OR(F368="",F368=0),"",(N(P368)+N(H368)+N(Q368)+N(I368))/F368*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -13479,6 +15763,12 @@
         <f>IF(OR(M369="",F369=0),"",M369/F369*10000)</f>
         <v/>
       </c>
+      <c r="P369" s="7" t="n"/>
+      <c r="Q369" s="7" t="n"/>
+      <c r="R369" s="3">
+        <f>IF(OR(F369="",F369=0),"",(N(P369)+N(H369)+N(Q369)+N(I369))/F369*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -13511,6 +15801,12 @@
         <f>IF(OR(M370="",F370=0),"",M370/F370*10000)</f>
         <v/>
       </c>
+      <c r="P370" s="7" t="n"/>
+      <c r="Q370" s="7" t="n"/>
+      <c r="R370" s="3">
+        <f>IF(OR(F370="",F370=0),"",(N(P370)+N(H370)+N(Q370)+N(I370))/F370*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -13543,6 +15839,12 @@
         <f>IF(OR(M371="",F371=0),"",M371/F371*10000)</f>
         <v/>
       </c>
+      <c r="P371" s="7" t="n"/>
+      <c r="Q371" s="7" t="n"/>
+      <c r="R371" s="3">
+        <f>IF(OR(F371="",F371=0),"",(N(P371)+N(H371)+N(Q371)+N(I371))/F371*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -13575,6 +15877,12 @@
         <f>IF(OR(M372="",F372=0),"",M372/F372*10000)</f>
         <v/>
       </c>
+      <c r="P372" s="7" t="n"/>
+      <c r="Q372" s="7" t="n"/>
+      <c r="R372" s="3">
+        <f>IF(OR(F372="",F372=0),"",(N(P372)+N(H372)+N(Q372)+N(I372))/F372*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -13607,6 +15915,12 @@
         <f>IF(OR(M373="",F373=0),"",M373/F373*10000)</f>
         <v/>
       </c>
+      <c r="P373" s="7" t="n"/>
+      <c r="Q373" s="7" t="n"/>
+      <c r="R373" s="3">
+        <f>IF(OR(F373="",F373=0),"",(N(P373)+N(H373)+N(Q373)+N(I373))/F373*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -13639,6 +15953,12 @@
         <f>IF(OR(M374="",F374=0),"",M374/F374*10000)</f>
         <v/>
       </c>
+      <c r="P374" s="7" t="n"/>
+      <c r="Q374" s="7" t="n"/>
+      <c r="R374" s="3">
+        <f>IF(OR(F374="",F374=0),"",(N(P374)+N(H374)+N(Q374)+N(I374))/F374*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -13671,6 +15991,12 @@
         <f>IF(OR(M375="",F375=0),"",M375/F375*10000)</f>
         <v/>
       </c>
+      <c r="P375" s="7" t="n"/>
+      <c r="Q375" s="7" t="n"/>
+      <c r="R375" s="3">
+        <f>IF(OR(F375="",F375=0),"",(N(P375)+N(H375)+N(Q375)+N(I375))/F375*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -13703,6 +16029,12 @@
         <f>IF(OR(M376="",F376=0),"",M376/F376*10000)</f>
         <v/>
       </c>
+      <c r="P376" s="7" t="n"/>
+      <c r="Q376" s="7" t="n"/>
+      <c r="R376" s="3">
+        <f>IF(OR(F376="",F376=0),"",(N(P376)+N(H376)+N(Q376)+N(I376))/F376*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -13735,6 +16067,12 @@
         <f>IF(OR(M377="",F377=0),"",M377/F377*10000)</f>
         <v/>
       </c>
+      <c r="P377" s="7" t="n"/>
+      <c r="Q377" s="7" t="n"/>
+      <c r="R377" s="3">
+        <f>IF(OR(F377="",F377=0),"",(N(P377)+N(H377)+N(Q377)+N(I377))/F377*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -13767,6 +16105,12 @@
         <f>IF(OR(M378="",F378=0),"",M378/F378*10000)</f>
         <v/>
       </c>
+      <c r="P378" s="7" t="n"/>
+      <c r="Q378" s="7" t="n"/>
+      <c r="R378" s="3">
+        <f>IF(OR(F378="",F378=0),"",(N(P378)+N(H378)+N(Q378)+N(I378))/F378*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -13799,6 +16143,12 @@
         <f>IF(OR(M379="",F379=0),"",M379/F379*10000)</f>
         <v/>
       </c>
+      <c r="P379" s="7" t="n"/>
+      <c r="Q379" s="7" t="n"/>
+      <c r="R379" s="3">
+        <f>IF(OR(F379="",F379=0),"",(N(P379)+N(H379)+N(Q379)+N(I379))/F379*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -13831,6 +16181,12 @@
         <f>IF(OR(M380="",F380=0),"",M380/F380*10000)</f>
         <v/>
       </c>
+      <c r="P380" s="7" t="n"/>
+      <c r="Q380" s="7" t="n"/>
+      <c r="R380" s="3">
+        <f>IF(OR(F380="",F380=0),"",(N(P380)+N(H380)+N(Q380)+N(I380))/F380*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -13863,6 +16219,12 @@
         <f>IF(OR(M381="",F381=0),"",M381/F381*10000)</f>
         <v/>
       </c>
+      <c r="P381" s="7" t="n"/>
+      <c r="Q381" s="7" t="n"/>
+      <c r="R381" s="3">
+        <f>IF(OR(F381="",F381=0),"",(N(P381)+N(H381)+N(Q381)+N(I381))/F381*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -13895,6 +16257,12 @@
         <f>IF(OR(M382="",F382=0),"",M382/F382*10000)</f>
         <v/>
       </c>
+      <c r="P382" s="7" t="n"/>
+      <c r="Q382" s="7" t="n"/>
+      <c r="R382" s="3">
+        <f>IF(OR(F382="",F382=0),"",(N(P382)+N(H382)+N(Q382)+N(I382))/F382*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -13927,6 +16295,12 @@
         <f>IF(OR(M383="",F383=0),"",M383/F383*10000)</f>
         <v/>
       </c>
+      <c r="P383" s="7" t="n"/>
+      <c r="Q383" s="7" t="n"/>
+      <c r="R383" s="3">
+        <f>IF(OR(F383="",F383=0),"",(N(P383)+N(H383)+N(Q383)+N(I383))/F383*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -13959,6 +16333,12 @@
         <f>IF(OR(M384="",F384=0),"",M384/F384*10000)</f>
         <v/>
       </c>
+      <c r="P384" s="7" t="n"/>
+      <c r="Q384" s="7" t="n"/>
+      <c r="R384" s="3">
+        <f>IF(OR(F384="",F384=0),"",(N(P384)+N(H384)+N(Q384)+N(I384))/F384*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -13991,6 +16371,12 @@
         <f>IF(OR(M385="",F385=0),"",M385/F385*10000)</f>
         <v/>
       </c>
+      <c r="P385" s="7" t="n"/>
+      <c r="Q385" s="7" t="n"/>
+      <c r="R385" s="3">
+        <f>IF(OR(F385="",F385=0),"",(N(P385)+N(H385)+N(Q385)+N(I385))/F385*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -14023,6 +16409,12 @@
         <f>IF(OR(M386="",F386=0),"",M386/F386*10000)</f>
         <v/>
       </c>
+      <c r="P386" s="7" t="n"/>
+      <c r="Q386" s="7" t="n"/>
+      <c r="R386" s="3">
+        <f>IF(OR(F386="",F386=0),"",(N(P386)+N(H386)+N(Q386)+N(I386))/F386*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -14055,6 +16447,12 @@
         <f>IF(OR(M387="",F387=0),"",M387/F387*10000)</f>
         <v/>
       </c>
+      <c r="P387" s="7" t="n"/>
+      <c r="Q387" s="7" t="n"/>
+      <c r="R387" s="3">
+        <f>IF(OR(F387="",F387=0),"",(N(P387)+N(H387)+N(Q387)+N(I387))/F387*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -14087,6 +16485,12 @@
         <f>IF(OR(M388="",F388=0),"",M388/F388*10000)</f>
         <v/>
       </c>
+      <c r="P388" s="7" t="n"/>
+      <c r="Q388" s="7" t="n"/>
+      <c r="R388" s="3">
+        <f>IF(OR(F388="",F388=0),"",(N(P388)+N(H388)+N(Q388)+N(I388))/F388*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -14119,6 +16523,12 @@
         <f>IF(OR(M389="",F389=0),"",M389/F389*10000)</f>
         <v/>
       </c>
+      <c r="P389" s="7" t="n"/>
+      <c r="Q389" s="7" t="n"/>
+      <c r="R389" s="3">
+        <f>IF(OR(F389="",F389=0),"",(N(P389)+N(H389)+N(Q389)+N(I389))/F389*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -14151,6 +16561,12 @@
         <f>IF(OR(M390="",F390=0),"",M390/F390*10000)</f>
         <v/>
       </c>
+      <c r="P390" s="7" t="n"/>
+      <c r="Q390" s="7" t="n"/>
+      <c r="R390" s="3">
+        <f>IF(OR(F390="",F390=0),"",(N(P390)+N(H390)+N(Q390)+N(I390))/F390*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -14183,6 +16599,12 @@
         <f>IF(OR(M391="",F391=0),"",M391/F391*10000)</f>
         <v/>
       </c>
+      <c r="P391" s="7" t="n"/>
+      <c r="Q391" s="7" t="n"/>
+      <c r="R391" s="3">
+        <f>IF(OR(F391="",F391=0),"",(N(P391)+N(H391)+N(Q391)+N(I391))/F391*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -14215,6 +16637,12 @@
         <f>IF(OR(M392="",F392=0),"",M392/F392*10000)</f>
         <v/>
       </c>
+      <c r="P392" s="7" t="n"/>
+      <c r="Q392" s="7" t="n"/>
+      <c r="R392" s="3">
+        <f>IF(OR(F392="",F392=0),"",(N(P392)+N(H392)+N(Q392)+N(I392))/F392*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -14247,6 +16675,12 @@
         <f>IF(OR(M393="",F393=0),"",M393/F393*10000)</f>
         <v/>
       </c>
+      <c r="P393" s="7" t="n"/>
+      <c r="Q393" s="7" t="n"/>
+      <c r="R393" s="3">
+        <f>IF(OR(F393="",F393=0),"",(N(P393)+N(H393)+N(Q393)+N(I393))/F393*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -14279,6 +16713,12 @@
         <f>IF(OR(M394="",F394=0),"",M394/F394*10000)</f>
         <v/>
       </c>
+      <c r="P394" s="7" t="n"/>
+      <c r="Q394" s="7" t="n"/>
+      <c r="R394" s="3">
+        <f>IF(OR(F394="",F394=0),"",(N(P394)+N(H394)+N(Q394)+N(I394))/F394*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -14311,6 +16751,12 @@
         <f>IF(OR(M395="",F395=0),"",M395/F395*10000)</f>
         <v/>
       </c>
+      <c r="P395" s="7" t="n"/>
+      <c r="Q395" s="7" t="n"/>
+      <c r="R395" s="3">
+        <f>IF(OR(F395="",F395=0),"",(N(P395)+N(H395)+N(Q395)+N(I395))/F395*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -14343,6 +16789,12 @@
         <f>IF(OR(M396="",F396=0),"",M396/F396*10000)</f>
         <v/>
       </c>
+      <c r="P396" s="7" t="n"/>
+      <c r="Q396" s="7" t="n"/>
+      <c r="R396" s="3">
+        <f>IF(OR(F396="",F396=0),"",(N(P396)+N(H396)+N(Q396)+N(I396))/F396*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -14375,6 +16827,12 @@
         <f>IF(OR(M397="",F397=0),"",M397/F397*10000)</f>
         <v/>
       </c>
+      <c r="P397" s="7" t="n"/>
+      <c r="Q397" s="7" t="n"/>
+      <c r="R397" s="3">
+        <f>IF(OR(F397="",F397=0),"",(N(P397)+N(H397)+N(Q397)+N(I397))/F397*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -14407,6 +16865,12 @@
         <f>IF(OR(M398="",F398=0),"",M398/F398*10000)</f>
         <v/>
       </c>
+      <c r="P398" s="7" t="n"/>
+      <c r="Q398" s="7" t="n"/>
+      <c r="R398" s="3">
+        <f>IF(OR(F398="",F398=0),"",(N(P398)+N(H398)+N(Q398)+N(I398))/F398*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -14439,6 +16903,12 @@
         <f>IF(OR(M399="",F399=0),"",M399/F399*10000)</f>
         <v/>
       </c>
+      <c r="P399" s="7" t="n"/>
+      <c r="Q399" s="7" t="n"/>
+      <c r="R399" s="3">
+        <f>IF(OR(F399="",F399=0),"",(N(P399)+N(H399)+N(Q399)+N(I399))/F399*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -14471,6 +16941,12 @@
         <f>IF(OR(M400="",F400=0),"",M400/F400*10000)</f>
         <v/>
       </c>
+      <c r="P400" s="7" t="n"/>
+      <c r="Q400" s="7" t="n"/>
+      <c r="R400" s="3">
+        <f>IF(OR(F400="",F400=0),"",(N(P400)+N(H400)+N(Q400)+N(I400))/F400*1000)</f>
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="7" t="n"/>
@@ -14501,6 +16977,12 @@
       </c>
       <c r="O401" s="3">
         <f>IF(OR(M401="",F401=0),"",M401/F401*10000)</f>
+        <v/>
+      </c>
+      <c r="P401" s="7" t="n"/>
+      <c r="Q401" s="7" t="n"/>
+      <c r="R401" s="3">
+        <f>IF(OR(F401="",F401=0),"",(N(P401)+N(H401)+N(Q401)+N(I401))/F401*1000)</f>
         <v/>
       </c>
     </row>
